--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_32_48.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_32_48.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4518934.115227968</v>
+        <v>4491041.615361019</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12505018.6593289</v>
+        <v>12505018.65932889</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12505018.6593289</v>
+        <v>12505018.65932889</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32592282.92039121</v>
+        <v>32592282.92039122</v>
       </c>
     </row>
   </sheetData>
@@ -663,13 +663,13 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>2.67998535234284</v>
+        <v>360.1678862607644</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>444.6011368983566</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>363.9523417085426</v>
       </c>
       <c r="L2" t="n">
-        <v>330.9802613065326</v>
+        <v>294.6561297084554</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -696,13 +696,13 @@
         <v>389.7202916846452</v>
       </c>
       <c r="P2" t="n">
-        <v>346.3574721009829</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>472.3008380094826</v>
+        <v>491.0301</v>
       </c>
       <c r="R2" t="n">
-        <v>117.3194440587915</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>70.29721302845354</v>
@@ -714,7 +714,7 @@
         <v>249.1351055938368</v>
       </c>
       <c r="V2" t="n">
-        <v>229.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>238.3734759809475</v>
@@ -723,7 +723,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>111.3174326828064</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -745,7 +745,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>197.2792160800278</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,10 +781,10 @@
         <v>99.49556697727203</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>471.5186003823892</v>
       </c>
       <c r="S3" t="n">
-        <v>37.81151004136654</v>
+        <v>55.85664147404526</v>
       </c>
       <c r="T3" t="n">
         <v>403.0342557835515</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>62.18656272264445</v>
       </c>
     </row>
     <row r="4">
@@ -894,16 +894,16 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>39.51466218646482</v>
       </c>
       <c r="G5" t="n">
         <v>402.6799853523428</v>
@@ -915,16 +915,16 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>444.6011368983566</v>
+        <v>14.29640031219986</v>
       </c>
       <c r="K5" t="n">
-        <v>206.3786017951107</v>
+        <v>300.2957662802843</v>
       </c>
       <c r="L5" t="n">
         <v>330.9802613065326</v>
       </c>
       <c r="M5" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>501</v>
@@ -933,19 +933,19 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>346.3574721009829</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>491.0301</v>
       </c>
       <c r="R5" t="n">
-        <v>126.572362373672</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>70.29721302845356</v>
+        <v>15.08083171543239</v>
       </c>
       <c r="T5" t="n">
-        <v>181.9593204220312</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>249.1351055938368</v>
@@ -954,10 +954,10 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
-        <v>238.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>192.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -979,19 +979,19 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.1630830448387</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>326.6007664317041</v>
       </c>
       <c r="I6" t="n">
-        <v>197.2792160800278</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,19 +1018,19 @@
         <v>99.49556697727203</v>
       </c>
       <c r="R6" t="n">
-        <v>126.5465569728771</v>
+        <v>501</v>
       </c>
       <c r="S6" t="n">
-        <v>55.85664147404527</v>
+        <v>455.8566414740453</v>
       </c>
       <c r="T6" t="n">
         <v>3.034255783551552</v>
       </c>
       <c r="U6" t="n">
-        <v>400.1724352318848</v>
+        <v>0.1724352318848609</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>120.6150638648498</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1137,19 +1137,19 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>4.363289606868648</v>
+        <v>219.2868625093214</v>
       </c>
       <c r="F8" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G8" t="n">
-        <v>2.679985352342844</v>
+        <v>2.67998535234284</v>
       </c>
       <c r="H8" t="n">
-        <v>396.9758697588038</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>108.5451998836896</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>444.6011368983566</v>
@@ -1161,31 +1161,31 @@
         <v>330.9802613065327</v>
       </c>
       <c r="M8" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>343.4262600865679</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>389.7202916846452</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>346.3574721009829</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>108.3484963009398</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>13.7133038391448</v>
       </c>
       <c r="S8" t="n">
-        <v>70.29721302845356</v>
+        <v>70.29721302845354</v>
       </c>
       <c r="T8" t="n">
         <v>181.9593204220312</v>
       </c>
       <c r="U8" t="n">
-        <v>260.9334800101349</v>
+        <v>249.1351055938368</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1197,7 +1197,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>111.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1207,19 +1207,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>61.2913133524359</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1252,25 +1252,25 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>99.49556697727203</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>501</v>
       </c>
       <c r="S9" t="n">
-        <v>455.8566414740453</v>
+        <v>55.85664147404526</v>
       </c>
       <c r="T9" t="n">
-        <v>223.0167594548842</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>400.1724352318848</v>
+        <v>0.1724352318848332</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>180.9758697588038</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>254.2972130284535</v>
       </c>
       <c r="T11" t="n">
         <v>365.9593204220312</v>
@@ -1428,13 +1428,13 @@
         <v>413.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>422.3734759809475</v>
+        <v>0.744834347244282</v>
       </c>
       <c r="X11" t="n">
-        <v>308.9618738363605</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>295.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1450,7 +1450,7 @@
         <v>145.0999124455193</v>
       </c>
       <c r="D12" t="n">
-        <v>131.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>126.6720972219126</v>
@@ -1459,10 +1459,10 @@
         <v>123.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>109.1630830448387</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>110.6007664317041</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>295.4831557829453</v>
       </c>
       <c r="S12" t="n">
-        <v>71.64296455564042</v>
+        <v>239.8566414740453</v>
       </c>
       <c r="T12" t="n">
         <v>187.0342557835515</v>
@@ -1504,7 +1504,7 @@
         <v>184.1724352318849</v>
       </c>
       <c r="V12" t="n">
-        <v>198.5106671915202</v>
+        <v>86.5153708644156</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>8.474339216372716</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1562,13 +1562,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>351.5980530485281</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>332.7509039934457</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>10.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>149.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>105.5356905151289</v>
+        <v>143.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>143.8896287080119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>135.9758697588038</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,25 +1653,25 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>209.2972130284535</v>
       </c>
       <c r="T14" t="n">
-        <v>320.9593204220312</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>368.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>377.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>331.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>250.3174326828064</v>
+        <v>52.80889433195225</v>
       </c>
     </row>
     <row r="15">
@@ -1696,10 +1696,10 @@
         <v>78.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>64.16308304483869</v>
+        <v>64.16308304483866</v>
       </c>
       <c r="H15" t="n">
-        <v>65.60076643170413</v>
+        <v>65.60076643170414</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
         <v>142.0342557835515</v>
       </c>
       <c r="U15" t="n">
-        <v>139.1724352318848</v>
+        <v>139.1724352318849</v>
       </c>
       <c r="V15" t="n">
         <v>153.5106671915202</v>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>24.53621805555548</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>236.2302555995537</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>14.17630416758268</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>162.4906332855948</v>
+        <v>424.371266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>443.8721607680363</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>92.95125019465871</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>184.9993129555745</v>
       </c>
       <c r="C17" t="n">
-        <v>52.91189151442386</v>
+        <v>152.4745782429939</v>
       </c>
       <c r="D17" t="n">
         <v>113.3391557398498</v>
@@ -1854,7 +1854,7 @@
         <v>107.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>105.6799853523428</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>99.9758697588038</v>
@@ -1893,22 +1893,22 @@
         <v>173.2972130284535</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>284.9593204220312</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>352.1351055938368</v>
       </c>
       <c r="V17" t="n">
-        <v>332.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>341.3734759809475</v>
       </c>
       <c r="X17" t="n">
-        <v>295.2818334606677</v>
+        <v>26.47384996262798</v>
       </c>
       <c r="Y17" t="n">
-        <v>214.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1918,19 +1918,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>87.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
         <v>64.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>279.2739243921778</v>
+        <v>50.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>45.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>42.63624233787687</v>
+        <v>270.9724798323516</v>
       </c>
       <c r="G18" t="n">
         <v>28.16308304483866</v>
@@ -2030,22 +2030,22 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>147.8754802550089</v>
       </c>
       <c r="N19" t="n">
-        <v>200.2302555995537</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>275.1363181773756</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>331.9975366725398</v>
       </c>
       <c r="Q19" t="n">
         <v>388.371266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>280.34129248695</v>
+        <v>0.6985311589549088</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2076,25 +2076,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>184.9993129555745</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>152.4745782429939</v>
       </c>
       <c r="D20" t="n">
-        <v>113.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>107.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>107.8896287080119</v>
       </c>
       <c r="G20" t="n">
         <v>105.6799853523428</v>
       </c>
       <c r="H20" t="n">
-        <v>99.97586975880381</v>
+        <v>20.64672149084831</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>18.68502952469618</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>284.9593204220312</v>
@@ -2139,7 +2139,7 @@
         <v>332.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>341.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>295.2818334606677</v>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>315.8927941408032</v>
+        <v>87.55655664632661</v>
       </c>
       <c r="C21" t="n">
         <v>64.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>50.93768689770263</v>
+        <v>179.7783574149058</v>
       </c>
       <c r="E21" t="n">
         <v>45.67209722191262</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>99.49556697727203</v>
       </c>
       <c r="R21" t="n">
         <v>214.4831557829453</v>
@@ -2212,10 +2212,10 @@
         <v>106.0342557835515</v>
       </c>
       <c r="U21" t="n">
-        <v>103.1724352318848</v>
+        <v>400.1724352318848</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>117.5106671915202</v>
       </c>
       <c r="W21" t="n">
         <v>135.3731429098285</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>54.69726750204148</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>147.8754802550089</v>
@@ -2279,13 +2279,13 @@
         <v>331.9975366725398</v>
       </c>
       <c r="Q22" t="n">
-        <v>134.1422744829577</v>
+        <v>131.8882917903405</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>56.95125019465871</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2313,22 +2313,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>92.87264988210626</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>152.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>113.3391557398498</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>107.3632896068686</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>107.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>97.1315999941999</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         <v>352.1351055938368</v>
       </c>
       <c r="V23" t="n">
-        <v>332.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>341.3734759809475</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>87.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>64.09991244551929</v>
       </c>
       <c r="D24" t="n">
         <v>50.93768689770263</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>99.49556697727203</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>214.4831557829453</v>
@@ -2449,10 +2449,10 @@
         <v>106.0342557835516</v>
       </c>
       <c r="U24" t="n">
-        <v>232.0131057490886</v>
+        <v>103.1724352318849</v>
       </c>
       <c r="V24" t="n">
-        <v>117.5106671915202</v>
+        <v>345.8469046859954</v>
       </c>
       <c r="W24" t="n">
         <v>135.3731429098285</v>
@@ -2501,28 +2501,28 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>54.69726750204147</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>147.8754802550089</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>200.2302555995537</v>
+        <v>129.0731170715255</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>275.1363181773756</v>
       </c>
       <c r="P25" t="n">
-        <v>295.9536127126164</v>
+        <v>331.9975366725398</v>
       </c>
       <c r="Q25" t="n">
-        <v>388.371266425598</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>407.8721607680363</v>
       </c>
       <c r="S25" t="n">
-        <v>56.95125019465871</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2550,19 +2550,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>105.250008206869</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>164.0000000000043</v>
+        <v>164.000000000107</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>164.0000000000996</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>164.0000000000998</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2598,19 +2598,19 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>39.2011917931186</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>144.4511999996936</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>164.0000000000038</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>164.0000000000043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>164.000000000107</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>164.000000000107</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2647,10 +2647,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>164.0000000001563</v>
       </c>
       <c r="I27" t="n">
-        <v>53.27921608002778</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>164.0000000000101</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>91.17198391994219</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>164.0000000000099</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>164.0000000000099</v>
+        <v>144.4511999996296</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2726,10 +2726,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>80.47433921637271</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>18.09994742339697</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>52.64879740427648</v>
+        <v>63.95964847347082</v>
       </c>
       <c r="U28" t="n">
-        <v>6.932030618720233</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>57.99557134250163</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2793,16 +2793,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>164.0000000001407</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>164.0000000000063</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>144.2500082068509</v>
+        <v>164.0000000002094</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2844,19 +2844,19 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>164.0000000000144</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>164.0000000000098</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>164.0000000001405</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>144.2500082063908</v>
       </c>
     </row>
     <row r="30">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>164.0000000000108</v>
+        <v>164.0000000001407</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>164.0000000001406</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2878,16 +2878,16 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>156.6362423378769</v>
+        <v>144.4511999995081</v>
       </c>
       <c r="G30" t="n">
-        <v>142.1630830448387</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>14.27921608002778</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>164.0000000002104</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>159.3726585372458</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>7.176019104333739</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2996,19 +2996,19 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>86.6732505761515</v>
+        <v>164.0000000002145</v>
       </c>
       <c r="T31" t="n">
-        <v>24.95964847347083</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>16.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>43.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3024,16 +3024,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>164.0000000000115</v>
+        <v>164.0000000000374</v>
       </c>
       <c r="C32" t="n">
-        <v>144.2500082068457</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>164.0000000000098</v>
+        <v>164.0000000000374</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -3042,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>164.0000000000143</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>144.2500082067693</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>164.0000000000374</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>164.0000000000121</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>164.0000000001625</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -3121,10 +3121,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>130.1719839199279</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>14.27921608002778</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3151,25 +3151,25 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>164.0000000000154</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>164.0000000000168</v>
+        <v>144.4511999995129</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>164.0000000001623</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>164.0000000001623</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>104.1138003370787</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3194,13 +3194,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>25.11265642314604</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>61.56059415300544</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>41.47433921637273</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3221,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>92.36624776762604</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>24.95964847347082</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         <v>16.17031021621619</v>
       </c>
       <c r="W34" t="n">
-        <v>43.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3264,22 +3264,22 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>164.0000000000126</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>164.0000000000447</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>144.2500082067474</v>
       </c>
       <c r="G35" t="n">
-        <v>164.0000000000162</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>144.250008206841</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0.2011917931185963</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>164.0000000000447</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>164.0000000000447</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>164.0000000000116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3343,25 +3343,25 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>164.0000000002098</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>144.4511999992265</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>142.1630830448387</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>14.27921608002778</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>152.0089008751096</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -3397,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>164.000000000354</v>
       </c>
       <c r="V36" t="n">
-        <v>164.0000000000128</v>
+        <v>164.0000000002096</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>164.000000000011</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>48.65035832092092</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -3428,16 +3428,16 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>38.66320444711928</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>91.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>41.47433921637271</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -3473,13 +3473,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>24.95964847347083</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>16.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -3504,13 +3504,13 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>164.0000000002535</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>164.000000000239</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3555,16 +3555,16 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>164.0000000000181</v>
+        <v>144.2500082061356</v>
       </c>
       <c r="V38" t="n">
-        <v>164.0000000000143</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>164.0000000000133</v>
+        <v>164.0000000002533</v>
       </c>
       <c r="X38" t="n">
-        <v>144.2500082068357</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -3583,22 +3583,22 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>151.8149576616165</v>
       </c>
       <c r="E39" t="n">
-        <v>159.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>156.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>142.1630830448387</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>143.6007664317041</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>14.27921608002778</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3637,13 +3637,13 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>164.0000000000142</v>
+        <v>164.0000000002533</v>
       </c>
       <c r="W39" t="n">
-        <v>12.73603722150255</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>164.0000000002533</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>164.0000000004353</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -3701,25 +3701,25 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>86.67325057615145</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>7.176019104112867</v>
       </c>
       <c r="T40" t="n">
-        <v>24.95964847347082</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>16.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>43.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>81.25000820685906</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>164.0000000002746</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>164.0000000000057</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>164.0000000004461</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>144.4511999990049</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,13 +3783,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>63.2011917931186</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>164.0000000000111</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>164.0000000002744</v>
       </c>
       <c r="X41" t="n">
-        <v>164.0000000000056</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3820,10 +3820,10 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>67.17198391995009</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>164.0000000002601</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3832,10 +3832,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>164.0000000004548</v>
       </c>
       <c r="I42" t="n">
-        <v>77.27921608002778</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>164.0000000000103</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>164.0000000004487</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>164.0000000000064</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>164.0000000000055</v>
+        <v>144.4511999988363</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>85.60073662064917</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>116.5327672393694</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>30.93203061872023</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -3975,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>164.0000000002008</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -3984,13 +3984,13 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>164.0000000000046</v>
+        <v>164.0000000002009</v>
       </c>
       <c r="G44" t="n">
-        <v>164.0000000000057</v>
+        <v>164.0000000002513</v>
       </c>
       <c r="H44" t="n">
-        <v>161.250008206871</v>
+        <v>144.451199999347</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>147.2011917931186</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>164.0000000002081</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>144.4511999992986</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4066,13 +4066,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>164.0000000002853</v>
       </c>
       <c r="H45" t="n">
-        <v>164.0000000000043</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>161.2792160800278</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>63.49556697727203</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -4114,13 +4114,13 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>83.67641694269322</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>164.0000000000026</v>
+        <v>164.0000000002079</v>
       </c>
     </row>
     <row r="46">
@@ -4151,43 +4151,43 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
         <v>34.20436723936942</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>516.5917552020879</v>
+        <v>473.6502409681703</v>
       </c>
       <c r="C2" t="n">
-        <v>466.6174337445183</v>
+        <v>423.6759195106007</v>
       </c>
       <c r="D2" t="n">
-        <v>456.1738420881044</v>
+        <v>413.2323278541868</v>
       </c>
       <c r="E2" t="n">
-        <v>47.72607480843909</v>
+        <v>408.8249646149255</v>
       </c>
       <c r="F2" t="n">
-        <v>42.78705591145741</v>
+        <v>403.8859457179439</v>
       </c>
       <c r="G2" t="n">
         <v>40.08</v>
@@ -4324,49 +4324,49 @@
         <v>86.97794252691256</v>
       </c>
       <c r="K2" t="n">
-        <v>582.9679425269126</v>
+        <v>215.3393145384855</v>
       </c>
       <c r="L2" t="n">
-        <v>744.6344462576876</v>
+        <v>413.6968602875204</v>
       </c>
       <c r="M2" t="n">
-        <v>1240.624446257688</v>
+        <v>909.6868602875204</v>
       </c>
       <c r="N2" t="n">
-        <v>1736.614446257688</v>
+        <v>1405.67686028752</v>
       </c>
       <c r="O2" t="n">
-        <v>1838.947585970167</v>
+        <v>1508.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1985.081553544932</v>
+        <v>2004</v>
       </c>
       <c r="Q2" t="n">
         <v>2004</v>
       </c>
       <c r="R2" t="n">
-        <v>1885.495511051726</v>
+        <v>2004</v>
       </c>
       <c r="S2" t="n">
-        <v>1814.488225164399</v>
+        <v>1932.992714112673</v>
       </c>
       <c r="T2" t="n">
-        <v>1630.690931808812</v>
+        <v>1749.195420757086</v>
       </c>
       <c r="U2" t="n">
-        <v>1379.039309996856</v>
+        <v>1497.54379894513</v>
       </c>
       <c r="V2" t="n">
-        <v>1146.866558313195</v>
+        <v>1497.54379894513</v>
       </c>
       <c r="W2" t="n">
-        <v>906.0852694435512</v>
+        <v>1256.762510075486</v>
       </c>
       <c r="X2" t="n">
-        <v>711.8611952408565</v>
+        <v>1062.538435872791</v>
       </c>
       <c r="Y2" t="n">
-        <v>599.4193440461027</v>
+        <v>556.477829812185</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>583.1396865182368</v>
+        <v>40.80083963146433</v>
       </c>
       <c r="C3" t="n">
-        <v>583.1396865182368</v>
+        <v>40.80083963146433</v>
       </c>
       <c r="D3" t="n">
-        <v>583.1396865182368</v>
+        <v>40.80083963146433</v>
       </c>
       <c r="E3" t="n">
-        <v>583.1396865182368</v>
+        <v>40.80083963146433</v>
       </c>
       <c r="F3" t="n">
-        <v>240.0727750658358</v>
+        <v>40.80083963146433</v>
       </c>
       <c r="G3" t="n">
-        <v>240.0727750658358</v>
+        <v>40.80083963146433</v>
       </c>
       <c r="H3" t="n">
-        <v>240.0727750658358</v>
+        <v>40.80083963146433</v>
       </c>
       <c r="I3" t="n">
         <v>40.80083963146433</v>
@@ -4424,28 +4424,28 @@
         <v>1903.499427295685</v>
       </c>
       <c r="R3" t="n">
-        <v>1903.499427295685</v>
+        <v>1427.218012768019</v>
       </c>
       <c r="S3" t="n">
-        <v>1865.305982809456</v>
+        <v>1370.797162794236</v>
       </c>
       <c r="T3" t="n">
-        <v>1458.200673937182</v>
+        <v>963.6918539219615</v>
       </c>
       <c r="U3" t="n">
-        <v>1053.986092894874</v>
+        <v>559.4772728796536</v>
       </c>
       <c r="V3" t="n">
-        <v>1039.32885330748</v>
+        <v>544.8200332922595</v>
       </c>
       <c r="W3" t="n">
-        <v>1006.628708954118</v>
+        <v>512.1198889388974</v>
       </c>
       <c r="X3" t="n">
-        <v>986.5653357769584</v>
+        <v>492.0565157617382</v>
       </c>
       <c r="Y3" t="n">
-        <v>583.1396865182368</v>
+        <v>429.2418059408852</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="C4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="D4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="E4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="F4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="H4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="I4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="J4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="K4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="L4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="M4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="O4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="P4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="R4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="S4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="T4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="U4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="V4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="W4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="X4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2004</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="5">
@@ -4534,16 +4534,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>507.2453730658449</v>
+        <v>1309.673023116693</v>
       </c>
       <c r="C5" t="n">
-        <v>457.2710516082753</v>
+        <v>1309.673023116693</v>
       </c>
       <c r="D5" t="n">
-        <v>446.8274599518614</v>
+        <v>895.1890274198751</v>
       </c>
       <c r="E5" t="n">
-        <v>446.8274599518614</v>
+        <v>486.7412601402098</v>
       </c>
       <c r="F5" t="n">
         <v>446.8274599518614</v>
@@ -4558,52 +4558,52 @@
         <v>40.08</v>
       </c>
       <c r="J5" t="n">
-        <v>86.97794252691256</v>
+        <v>521.6291916038385</v>
       </c>
       <c r="K5" t="n">
-        <v>374.5047083904371</v>
+        <v>714.2901347550663</v>
       </c>
       <c r="L5" t="n">
-        <v>536.1712121212122</v>
+        <v>875.9566384858415</v>
       </c>
       <c r="M5" t="n">
-        <v>526.1006060606061</v>
+        <v>1371.946638485842</v>
       </c>
       <c r="N5" t="n">
-        <v>516.03</v>
+        <v>1361.876032425235</v>
       </c>
       <c r="O5" t="n">
-        <v>1012.02</v>
+        <v>1857.866032425235</v>
       </c>
       <c r="P5" t="n">
-        <v>1508.01</v>
+        <v>2004</v>
       </c>
       <c r="Q5" t="n">
         <v>2004</v>
       </c>
       <c r="R5" t="n">
-        <v>1876.149128915483</v>
+        <v>2004</v>
       </c>
       <c r="S5" t="n">
-        <v>1805.141843028156</v>
+        <v>1988.766836651078</v>
       </c>
       <c r="T5" t="n">
-        <v>1621.344549672569</v>
+        <v>1988.766836651078</v>
       </c>
       <c r="U5" t="n">
-        <v>1369.692927860613</v>
+        <v>1737.115214839122</v>
       </c>
       <c r="V5" t="n">
-        <v>1137.520176176952</v>
+        <v>1504.942463155462</v>
       </c>
       <c r="W5" t="n">
-        <v>896.7388873073082</v>
+        <v>1504.942463155462</v>
       </c>
       <c r="X5" t="n">
-        <v>702.5148131046135</v>
+        <v>1504.942463155462</v>
       </c>
       <c r="Y5" t="n">
-        <v>590.0729619098596</v>
+        <v>1392.500611960708</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1243.832689675236</v>
+        <v>369.9797640724284</v>
       </c>
       <c r="C6" t="n">
-        <v>1243.832689675236</v>
+        <v>369.9797640724284</v>
       </c>
       <c r="D6" t="n">
-        <v>1243.832689675236</v>
+        <v>369.9797640724284</v>
       </c>
       <c r="E6" t="n">
-        <v>897.6992581379502</v>
+        <v>369.9797640724284</v>
       </c>
       <c r="F6" t="n">
-        <v>897.6992581379502</v>
+        <v>369.9797640724284</v>
       </c>
       <c r="G6" t="n">
-        <v>569.2516995067999</v>
+        <v>369.9797640724284</v>
       </c>
       <c r="H6" t="n">
-        <v>239.3519354343715</v>
+        <v>40.08</v>
       </c>
       <c r="I6" t="n">
         <v>40.08</v>
@@ -4661,28 +4661,28 @@
         <v>1902.778587664221</v>
       </c>
       <c r="R6" t="n">
-        <v>1774.953782641112</v>
+        <v>1396.717981603615</v>
       </c>
       <c r="S6" t="n">
-        <v>1718.532932667329</v>
+        <v>936.2567275894274</v>
       </c>
       <c r="T6" t="n">
-        <v>1715.468027835459</v>
+        <v>933.1918227575571</v>
       </c>
       <c r="U6" t="n">
-        <v>1311.253446793151</v>
+        <v>933.0176457556532</v>
       </c>
       <c r="V6" t="n">
-        <v>1296.596207205757</v>
+        <v>811.1842479123706</v>
       </c>
       <c r="W6" t="n">
-        <v>1263.896062852395</v>
+        <v>778.4841035590084</v>
       </c>
       <c r="X6" t="n">
-        <v>1243.832689675236</v>
+        <v>758.4207303818492</v>
       </c>
       <c r="Y6" t="n">
-        <v>1243.832689675236</v>
+        <v>758.4207303818492</v>
       </c>
     </row>
     <row r="7">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>623.1786942349097</v>
+        <v>733.6862732853735</v>
       </c>
       <c r="C8" t="n">
-        <v>573.20437277734</v>
+        <v>683.7119518278039</v>
       </c>
       <c r="D8" t="n">
-        <v>562.7607811209261</v>
+        <v>673.26836017139</v>
       </c>
       <c r="E8" t="n">
-        <v>558.3534178816649</v>
+        <v>451.7664788488431</v>
       </c>
       <c r="F8" t="n">
-        <v>553.4143989846832</v>
+        <v>42.78705591145741</v>
       </c>
       <c r="G8" t="n">
-        <v>550.7073430732257</v>
+        <v>40.08</v>
       </c>
       <c r="H8" t="n">
-        <v>149.7216160441309</v>
+        <v>40.08</v>
       </c>
       <c r="I8" t="n">
         <v>40.08</v>
@@ -4804,43 +4804,43 @@
         <v>377.0058182692606</v>
       </c>
       <c r="M8" t="n">
-        <v>366.9352122086545</v>
+        <v>872.9958182692606</v>
       </c>
       <c r="N8" t="n">
-        <v>516.03</v>
+        <v>1368.985818269261</v>
       </c>
       <c r="O8" t="n">
-        <v>1012.02</v>
+        <v>1471.31895798174</v>
       </c>
       <c r="P8" t="n">
-        <v>1508.01</v>
+        <v>1617.452925556505</v>
       </c>
       <c r="Q8" t="n">
         <v>2004</v>
       </c>
       <c r="R8" t="n">
-        <v>2004</v>
+        <v>1990.148177940258</v>
       </c>
       <c r="S8" t="n">
-        <v>1932.992714112673</v>
+        <v>1919.140892052931</v>
       </c>
       <c r="T8" t="n">
-        <v>1749.195420757086</v>
+        <v>1735.343598697344</v>
       </c>
       <c r="U8" t="n">
-        <v>1485.626249029677</v>
+        <v>1483.691976885387</v>
       </c>
       <c r="V8" t="n">
-        <v>1253.453497346017</v>
+        <v>1251.519225201727</v>
       </c>
       <c r="W8" t="n">
-        <v>1012.672208476373</v>
+        <v>1010.737936332083</v>
       </c>
       <c r="X8" t="n">
-        <v>818.4481342736782</v>
+        <v>816.5138621293881</v>
       </c>
       <c r="Y8" t="n">
-        <v>706.0062830789243</v>
+        <v>816.5138621293881</v>
       </c>
     </row>
     <row r="9">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>239.3519354343715</v>
+        <v>1017.461948258268</v>
       </c>
       <c r="C9" t="n">
-        <v>239.3519354343715</v>
+        <v>652.714561949663</v>
       </c>
       <c r="D9" t="n">
-        <v>239.3519354343715</v>
+        <v>301.2623529620845</v>
       </c>
       <c r="E9" t="n">
-        <v>239.3519354343715</v>
+        <v>301.2623529620845</v>
       </c>
       <c r="F9" t="n">
         <v>239.3519354343715</v>
@@ -4895,31 +4895,31 @@
         <v>2003.279160368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1902.778587664221</v>
+        <v>2003.279160368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1396.717981603615</v>
+        <v>1497.218554307929</v>
       </c>
       <c r="S9" t="n">
-        <v>936.2567275894274</v>
+        <v>1440.797704334146</v>
       </c>
       <c r="T9" t="n">
-        <v>710.9872735945949</v>
+        <v>1440.797704334146</v>
       </c>
       <c r="U9" t="n">
-        <v>306.7726925522869</v>
+        <v>1440.623527332242</v>
       </c>
       <c r="V9" t="n">
-        <v>292.1154529648928</v>
+        <v>1425.966287744848</v>
       </c>
       <c r="W9" t="n">
-        <v>259.4153086115306</v>
+        <v>1425.966287744848</v>
       </c>
       <c r="X9" t="n">
-        <v>239.3519354343715</v>
+        <v>1405.902914567689</v>
       </c>
       <c r="Y9" t="n">
-        <v>239.3519354343715</v>
+        <v>1405.902914567689</v>
       </c>
     </row>
     <row r="10">
@@ -5008,49 +5008,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40.08</v>
+        <v>222.8839088472765</v>
       </c>
       <c r="C11" t="n">
-        <v>40.08</v>
+        <v>222.8839088472765</v>
       </c>
       <c r="D11" t="n">
-        <v>40.08</v>
+        <v>222.8839088472765</v>
       </c>
       <c r="E11" t="n">
-        <v>40.08</v>
+        <v>222.8839088472765</v>
       </c>
       <c r="F11" t="n">
-        <v>40.08</v>
+        <v>222.8839088472765</v>
       </c>
       <c r="G11" t="n">
-        <v>40.08</v>
+        <v>222.8839088472765</v>
       </c>
       <c r="H11" t="n">
         <v>40.08</v>
       </c>
       <c r="I11" t="n">
-        <v>146.4602521151473</v>
+        <v>40.08</v>
       </c>
       <c r="J11" t="n">
-        <v>416.1351265857742</v>
+        <v>95.91487447062691</v>
       </c>
       <c r="K11" t="n">
-        <v>743.7148840780899</v>
+        <v>231.5920561791696</v>
       </c>
       <c r="L11" t="n">
-        <v>1125.874425384623</v>
+        <v>544.9286642922513</v>
       </c>
       <c r="M11" t="n">
-        <v>1212.276166022959</v>
+        <v>544.9286642922514</v>
       </c>
       <c r="N11" t="n">
-        <v>1708.266166022959</v>
+        <v>544.9286642922514</v>
       </c>
       <c r="O11" t="n">
-        <v>1818.43307725516</v>
+        <v>1040.918664292251</v>
       </c>
       <c r="P11" t="n">
-        <v>1971.529179875187</v>
+        <v>1475.539179875187</v>
       </c>
       <c r="Q11" t="n">
         <v>1971.529179875187</v>
@@ -5059,25 +5059,25 @@
         <v>2004</v>
       </c>
       <c r="S11" t="n">
-        <v>2004</v>
+        <v>1747.134128254087</v>
       </c>
       <c r="T11" t="n">
-        <v>1634.344120785827</v>
+        <v>1377.478249039914</v>
       </c>
       <c r="U11" t="n">
-        <v>1196.833913115285</v>
+        <v>939.968041369372</v>
       </c>
       <c r="V11" t="n">
-        <v>778.8025755730384</v>
+        <v>521.9367038271257</v>
       </c>
       <c r="W11" t="n">
-        <v>352.1627008448086</v>
+        <v>521.1843459006163</v>
       </c>
       <c r="X11" t="n">
-        <v>40.08</v>
+        <v>521.1843459006163</v>
       </c>
       <c r="Y11" t="n">
-        <v>40.08</v>
+        <v>222.8839088472765</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>794.7363518985397</v>
+        <v>439.4822747528372</v>
       </c>
       <c r="C12" t="n">
-        <v>648.1707837717526</v>
+        <v>292.91670662605</v>
       </c>
       <c r="D12" t="n">
-        <v>514.9003929659923</v>
+        <v>292.91670662605</v>
       </c>
       <c r="E12" t="n">
-        <v>386.948779610525</v>
+        <v>164.9650932705827</v>
       </c>
       <c r="F12" t="n">
-        <v>262.0636863399423</v>
+        <v>40.08</v>
       </c>
       <c r="G12" t="n">
-        <v>151.7979458906103</v>
+        <v>40.08</v>
       </c>
       <c r="H12" t="n">
         <v>40.08</v>
       </c>
       <c r="I12" t="n">
-        <v>58.6135760807725</v>
+        <v>40.08</v>
       </c>
       <c r="J12" t="n">
-        <v>236.4876256900338</v>
+        <v>217.9540496092612</v>
       </c>
       <c r="K12" t="n">
-        <v>384.6819623029856</v>
+        <v>499.300511364022</v>
       </c>
       <c r="L12" t="n">
-        <v>779.9443729547895</v>
+        <v>995.290511364022</v>
       </c>
       <c r="M12" t="n">
-        <v>1010.624314697649</v>
+        <v>1004.79741960217</v>
       </c>
       <c r="N12" t="n">
-        <v>1292.331115154274</v>
+        <v>1286.504220058795</v>
       </c>
       <c r="O12" t="n">
-        <v>1667.154831366295</v>
+        <v>1782.494220058795</v>
       </c>
       <c r="P12" t="n">
-        <v>1888.660611307499</v>
+        <v>2004</v>
       </c>
       <c r="Q12" t="n">
         <v>2004</v>
       </c>
       <c r="R12" t="n">
-        <v>2004</v>
+        <v>1705.532165875813</v>
       </c>
       <c r="S12" t="n">
-        <v>1931.633369135717</v>
+        <v>1463.252730043444</v>
       </c>
       <c r="T12" t="n">
-        <v>1742.709878445261</v>
+        <v>1274.329239352988</v>
       </c>
       <c r="U12" t="n">
-        <v>1556.677115584771</v>
+        <v>1088.296476492498</v>
       </c>
       <c r="V12" t="n">
-        <v>1356.161290138791</v>
+        <v>1000.907212993088</v>
       </c>
       <c r="W12" t="n">
-        <v>1356.161290138791</v>
+        <v>1000.907212993088</v>
       </c>
       <c r="X12" t="n">
-        <v>1150.239331103046</v>
+        <v>794.9852539573433</v>
       </c>
       <c r="Y12" t="n">
-        <v>964.9955000261424</v>
+        <v>609.7414228804398</v>
       </c>
     </row>
     <row r="13">
@@ -5166,49 +5166,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>118.6410448890104</v>
+        <v>129.1186305846768</v>
       </c>
       <c r="C13" t="n">
-        <v>118.6410448890104</v>
+        <v>129.1186305846768</v>
       </c>
       <c r="D13" t="n">
-        <v>118.6410448890104</v>
+        <v>129.1186305846768</v>
       </c>
       <c r="E13" t="n">
-        <v>118.6410448890104</v>
+        <v>129.1186305846768</v>
       </c>
       <c r="F13" t="n">
-        <v>118.6410448890104</v>
+        <v>129.1186305846768</v>
       </c>
       <c r="G13" t="n">
-        <v>118.6410448890104</v>
+        <v>129.1186305846768</v>
       </c>
       <c r="H13" t="n">
-        <v>110.0811062866138</v>
+        <v>129.1186305846768</v>
       </c>
       <c r="I13" t="n">
-        <v>163.4421583374508</v>
+        <v>182.4796826355138</v>
       </c>
       <c r="J13" t="n">
-        <v>376.1920242358037</v>
+        <v>395.2295485338668</v>
       </c>
       <c r="K13" t="n">
-        <v>376.1920242358037</v>
+        <v>395.2295485338668</v>
       </c>
       <c r="L13" t="n">
-        <v>376.1920242358037</v>
+        <v>395.2295485338668</v>
       </c>
       <c r="M13" t="n">
-        <v>376.1920242358037</v>
+        <v>395.2295485338668</v>
       </c>
       <c r="N13" t="n">
-        <v>376.1920242358037</v>
+        <v>395.2295485338668</v>
       </c>
       <c r="O13" t="n">
-        <v>376.1920242358037</v>
+        <v>40.08</v>
       </c>
       <c r="P13" t="n">
-        <v>376.1920242358037</v>
+        <v>40.08</v>
       </c>
       <c r="Q13" t="n">
         <v>40.08</v>
@@ -5229,13 +5229,13 @@
         <v>129.1186305846768</v>
       </c>
       <c r="W13" t="n">
-        <v>118.6410448890104</v>
+        <v>129.1186305846768</v>
       </c>
       <c r="X13" t="n">
-        <v>118.6410448890104</v>
+        <v>129.1186305846768</v>
       </c>
       <c r="Y13" t="n">
-        <v>118.6410448890104</v>
+        <v>129.1186305846768</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>487.9077015131036</v>
+        <v>808.8098202591193</v>
       </c>
       <c r="C14" t="n">
-        <v>297.5293396514936</v>
+        <v>618.4314583975092</v>
       </c>
       <c r="D14" t="n">
-        <v>146.6817075910393</v>
+        <v>467.5838263370549</v>
       </c>
       <c r="E14" t="n">
-        <v>40.08</v>
+        <v>322.7724226937532</v>
       </c>
       <c r="F14" t="n">
-        <v>40.08</v>
+        <v>177.4293633927311</v>
       </c>
       <c r="G14" t="n">
-        <v>40.08</v>
+        <v>177.4293633927311</v>
       </c>
       <c r="H14" t="n">
         <v>40.08</v>
@@ -5269,52 +5269,52 @@
         <v>40.08</v>
       </c>
       <c r="J14" t="n">
-        <v>95.91487447062691</v>
+        <v>208.0027611498986</v>
       </c>
       <c r="K14" t="n">
-        <v>231.5920561791696</v>
+        <v>703.9927611498987</v>
       </c>
       <c r="L14" t="n">
-        <v>727.5820561791696</v>
+        <v>1199.982761149899</v>
       </c>
       <c r="M14" t="n">
-        <v>1223.57205617917</v>
+        <v>1199.982761149899</v>
       </c>
       <c r="N14" t="n">
-        <v>1719.56205617917</v>
+        <v>1199.982761149899</v>
       </c>
       <c r="O14" t="n">
-        <v>1829.728967411371</v>
+        <v>1695.972761149899</v>
       </c>
       <c r="P14" t="n">
-        <v>1982.825070031398</v>
+        <v>1849.068863769925</v>
       </c>
       <c r="Q14" t="n">
-        <v>1982.825070031398</v>
+        <v>1926.979179875187</v>
       </c>
       <c r="R14" t="n">
         <v>2004</v>
       </c>
       <c r="S14" t="n">
-        <v>2004</v>
+        <v>1792.588673708633</v>
       </c>
       <c r="T14" t="n">
-        <v>1679.798666240373</v>
+        <v>1792.588673708633</v>
       </c>
       <c r="U14" t="n">
-        <v>1679.798666240373</v>
+        <v>1792.588673708633</v>
       </c>
       <c r="V14" t="n">
-        <v>1679.798666240373</v>
+        <v>1420.011881620932</v>
       </c>
       <c r="W14" t="n">
-        <v>1298.613336966688</v>
+        <v>1420.011881620932</v>
       </c>
       <c r="X14" t="n">
-        <v>963.985222359953</v>
+        <v>1085.383767014197</v>
       </c>
       <c r="Y14" t="n">
-        <v>711.1393307611587</v>
+        <v>1032.041449507174</v>
       </c>
     </row>
     <row r="15">
@@ -5333,7 +5333,7 @@
         <v>333.0822111478104</v>
       </c>
       <c r="E15" t="n">
-        <v>250.5851432468886</v>
+        <v>250.5851432468885</v>
       </c>
       <c r="F15" t="n">
         <v>171.1545954308513</v>
@@ -5348,25 +5348,25 @@
         <v>40.08</v>
       </c>
       <c r="J15" t="n">
-        <v>40.08</v>
+        <v>217.9540496092612</v>
       </c>
       <c r="K15" t="n">
-        <v>231.3446544683565</v>
+        <v>499.300511364022</v>
       </c>
       <c r="L15" t="n">
-        <v>626.6070651201604</v>
+        <v>895.2837616472902</v>
       </c>
       <c r="M15" t="n">
-        <v>966.0743146976488</v>
+        <v>1125.963703390149</v>
       </c>
       <c r="N15" t="n">
-        <v>1247.781115154274</v>
+        <v>1407.670503846774</v>
       </c>
       <c r="O15" t="n">
-        <v>1622.604831366295</v>
+        <v>1782.494220058795</v>
       </c>
       <c r="P15" t="n">
-        <v>1844.110611307499</v>
+        <v>2004</v>
       </c>
       <c r="Q15" t="n">
         <v>2004</v>
@@ -5409,49 +5409,49 @@
         <v>310.4703398685478</v>
       </c>
       <c r="D16" t="n">
-        <v>310.4703398685478</v>
+        <v>285.6862812265725</v>
       </c>
       <c r="E16" t="n">
-        <v>310.4703398685478</v>
+        <v>285.6862812265725</v>
       </c>
       <c r="F16" t="n">
-        <v>310.4703398685478</v>
+        <v>285.6862812265725</v>
       </c>
       <c r="G16" t="n">
-        <v>326.7453516570724</v>
+        <v>301.9612930150972</v>
       </c>
       <c r="H16" t="n">
-        <v>362.9057558328634</v>
+        <v>338.1216971908882</v>
       </c>
       <c r="I16" t="n">
-        <v>460.8168078837004</v>
+        <v>436.0327492417252</v>
       </c>
       <c r="J16" t="n">
-        <v>718.1166737820533</v>
+        <v>693.3326151400781</v>
       </c>
       <c r="K16" t="n">
-        <v>746.4578224730201</v>
+        <v>721.6737638310449</v>
       </c>
       <c r="L16" t="n">
-        <v>746.4578224730201</v>
+        <v>721.6737638310449</v>
       </c>
       <c r="M16" t="n">
-        <v>746.4578224730201</v>
+        <v>721.6737638310449</v>
       </c>
       <c r="N16" t="n">
-        <v>746.4578224730201</v>
+        <v>483.0573440335158</v>
       </c>
       <c r="O16" t="n">
-        <v>746.4578224730201</v>
+        <v>468.7378448743414</v>
       </c>
       <c r="P16" t="n">
-        <v>746.4578224730201</v>
+        <v>468.7378448743414</v>
       </c>
       <c r="Q16" t="n">
-        <v>582.3258696592879</v>
+        <v>40.08</v>
       </c>
       <c r="R16" t="n">
-        <v>133.9701517117765</v>
+        <v>40.08</v>
       </c>
       <c r="S16" t="n">
         <v>40.08</v>
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>633.1707279598998</v>
+        <v>626.9916384409374</v>
       </c>
       <c r="C17" t="n">
-        <v>579.7243728948251</v>
+        <v>472.9769129429637</v>
       </c>
       <c r="D17" t="n">
-        <v>465.2403771980072</v>
+        <v>358.4929172461458</v>
       </c>
       <c r="E17" t="n">
-        <v>356.7926099183419</v>
+        <v>250.0451499664805</v>
       </c>
       <c r="F17" t="n">
-        <v>247.8131869809562</v>
+        <v>141.0657270290947</v>
       </c>
       <c r="G17" t="n">
         <v>141.0657270290947</v>
@@ -5518,13 +5518,13 @@
         <v>895.9015974857023</v>
       </c>
       <c r="N17" t="n">
-        <v>1244.746986147772</v>
+        <v>1354.913897379973</v>
       </c>
       <c r="O17" t="n">
-        <v>1354.913897379973</v>
+        <v>1850.903897379973</v>
       </c>
       <c r="P17" t="n">
-        <v>1508.01</v>
+        <v>2004</v>
       </c>
       <c r="Q17" t="n">
         <v>2004</v>
@@ -5536,22 +5536,22 @@
         <v>1828.952310072269</v>
       </c>
       <c r="T17" t="n">
-        <v>1828.952310072269</v>
+        <v>1541.114612676278</v>
       </c>
       <c r="U17" t="n">
-        <v>1828.952310072269</v>
+        <v>1185.422586823917</v>
       </c>
       <c r="V17" t="n">
-        <v>1492.739154348204</v>
+        <v>1185.422586823917</v>
       </c>
       <c r="W17" t="n">
-        <v>1147.917461438156</v>
+        <v>840.6008939138692</v>
       </c>
       <c r="X17" t="n">
-        <v>849.6529831950577</v>
+        <v>813.8596313253561</v>
       </c>
       <c r="Y17" t="n">
-        <v>633.1707279598998</v>
+        <v>813.8596313253561</v>
       </c>
     </row>
     <row r="18">
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>834.4699251252821</v>
+        <v>534.4699251252819</v>
       </c>
       <c r="C18" t="n">
-        <v>769.7225388166768</v>
+        <v>469.7225388166765</v>
       </c>
       <c r="D18" t="n">
-        <v>487.627665693265</v>
+        <v>418.270329829098</v>
       </c>
       <c r="E18" t="n">
-        <v>141.4942341559795</v>
+        <v>372.1368982918125</v>
       </c>
       <c r="F18" t="n">
         <v>98.42732270357861</v>
@@ -5591,13 +5591,13 @@
         <v>499.300511364022</v>
       </c>
       <c r="L18" t="n">
-        <v>885.5930678146171</v>
+        <v>894.562922015826</v>
       </c>
       <c r="M18" t="n">
-        <v>1116.273009557476</v>
+        <v>1116.273009557477</v>
       </c>
       <c r="N18" t="n">
-        <v>1397.979810014101</v>
+        <v>1397.979810014102</v>
       </c>
       <c r="O18" t="n">
         <v>1772.803526226122</v>
@@ -5624,13 +5624,13 @@
         <v>1287.180866304754</v>
       </c>
       <c r="W18" t="n">
-        <v>1150.440317910988</v>
+        <v>1150.440317910987</v>
       </c>
       <c r="X18" t="n">
         <v>1026.336540693424</v>
       </c>
       <c r="Y18" t="n">
-        <v>922.9108914347029</v>
+        <v>922.9108914347026</v>
       </c>
     </row>
     <row r="19">
@@ -5673,19 +5673,19 @@
         <v>1195.715487565129</v>
       </c>
       <c r="M19" t="n">
-        <v>1195.715487565129</v>
+        <v>1046.346315590372</v>
       </c>
       <c r="N19" t="n">
-        <v>993.4627041312359</v>
+        <v>1046.346315590372</v>
       </c>
       <c r="O19" t="n">
-        <v>715.547231224796</v>
+        <v>768.430842683932</v>
       </c>
       <c r="P19" t="n">
-        <v>715.547231224796</v>
+        <v>433.0797955399524</v>
       </c>
       <c r="Q19" t="n">
-        <v>323.2530227140909</v>
+        <v>40.78558702924738</v>
       </c>
       <c r="R19" t="n">
         <v>40.08</v>
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>362.2971826777742</v>
+        <v>539.1246499000663</v>
       </c>
       <c r="C20" t="n">
-        <v>362.2971826777742</v>
+        <v>385.1099244020926</v>
       </c>
       <c r="D20" t="n">
-        <v>247.8131869809562</v>
+        <v>385.1099244020926</v>
       </c>
       <c r="E20" t="n">
-        <v>247.8131869809562</v>
+        <v>276.6621571224273</v>
       </c>
       <c r="F20" t="n">
-        <v>247.8131869809562</v>
+        <v>167.6827341850416</v>
       </c>
       <c r="G20" t="n">
-        <v>141.0657270290948</v>
+        <v>60.93527423318011</v>
       </c>
       <c r="H20" t="n">
         <v>40.08</v>
@@ -5743,22 +5743,22 @@
         <v>40.08</v>
       </c>
       <c r="J20" t="n">
-        <v>521.9165636909221</v>
+        <v>95.91487447062691</v>
       </c>
       <c r="K20" t="n">
-        <v>657.5937453994648</v>
+        <v>516.03</v>
       </c>
       <c r="L20" t="n">
-        <v>825.9132867059975</v>
+        <v>1012.02</v>
       </c>
       <c r="M20" t="n">
-        <v>1244.746986147772</v>
+        <v>1012.02</v>
       </c>
       <c r="N20" t="n">
-        <v>1740.736986147772</v>
+        <v>1012.02</v>
       </c>
       <c r="O20" t="n">
-        <v>1850.903897379973</v>
+        <v>1508.01</v>
       </c>
       <c r="P20" t="n">
         <v>2004</v>
@@ -5770,25 +5770,25 @@
         <v>2004</v>
       </c>
       <c r="S20" t="n">
-        <v>1985.126232803337</v>
+        <v>2004</v>
       </c>
       <c r="T20" t="n">
-        <v>1697.288535407346</v>
+        <v>1716.162302604009</v>
       </c>
       <c r="U20" t="n">
-        <v>1341.596509554986</v>
+        <v>1360.470276751648</v>
       </c>
       <c r="V20" t="n">
-        <v>1005.383353830921</v>
+        <v>1024.257121027584</v>
       </c>
       <c r="W20" t="n">
-        <v>660.561660920873</v>
+        <v>1024.257121027584</v>
       </c>
       <c r="X20" t="n">
-        <v>362.2971826777742</v>
+        <v>725.992642784485</v>
       </c>
       <c r="Y20" t="n">
-        <v>362.2971826777742</v>
+        <v>725.992642784485</v>
       </c>
     </row>
     <row r="21">
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>303.8272609894487</v>
+        <v>433.9693524209671</v>
       </c>
       <c r="C21" t="n">
-        <v>239.0798746808434</v>
+        <v>369.2219661123618</v>
       </c>
       <c r="D21" t="n">
         <v>187.627665693265</v>
@@ -5822,52 +5822,52 @@
         <v>40.08</v>
       </c>
       <c r="J21" t="n">
-        <v>217.9540496092612</v>
+        <v>208.9841954080525</v>
       </c>
       <c r="K21" t="n">
-        <v>490.330657162815</v>
+        <v>490.3306571628133</v>
       </c>
       <c r="L21" t="n">
-        <v>885.593067814619</v>
+        <v>885.5930678146171</v>
       </c>
       <c r="M21" t="n">
-        <v>1116.273009557478</v>
+        <v>1116.273009557476</v>
       </c>
       <c r="N21" t="n">
-        <v>1397.979810014103</v>
+        <v>1397.979810014101</v>
       </c>
       <c r="O21" t="n">
-        <v>1772.803526226124</v>
+        <v>1772.803526226122</v>
       </c>
       <c r="P21" t="n">
-        <v>1994.309306167329</v>
+        <v>1994.309306167327</v>
       </c>
       <c r="Q21" t="n">
-        <v>1994.309306167329</v>
+        <v>1893.808733463012</v>
       </c>
       <c r="R21" t="n">
-        <v>1777.659653861323</v>
+        <v>1677.159081157006</v>
       </c>
       <c r="S21" t="n">
-        <v>1617.198399847136</v>
+        <v>1516.697827142819</v>
       </c>
       <c r="T21" t="n">
-        <v>1510.093090974862</v>
+        <v>1409.592518270545</v>
       </c>
       <c r="U21" t="n">
-        <v>1405.878509932554</v>
+        <v>1005.377937228237</v>
       </c>
       <c r="V21" t="n">
-        <v>987.1808663047557</v>
+        <v>886.680293600439</v>
       </c>
       <c r="W21" t="n">
-        <v>850.4403179109895</v>
+        <v>749.9397452066728</v>
       </c>
       <c r="X21" t="n">
-        <v>726.3365406934263</v>
+        <v>625.8359679891096</v>
       </c>
       <c r="Y21" t="n">
-        <v>622.9108914347046</v>
+        <v>522.410318730388</v>
       </c>
     </row>
     <row r="22">
@@ -5907,25 +5907,25 @@
         <v>1195.715487565129</v>
       </c>
       <c r="L22" t="n">
-        <v>1140.465722411551</v>
+        <v>1195.715487565129</v>
       </c>
       <c r="M22" t="n">
-        <v>991.0965504367948</v>
+        <v>1046.346315590372</v>
       </c>
       <c r="N22" t="n">
-        <v>788.8437670029022</v>
+        <v>844.0935321564795</v>
       </c>
       <c r="O22" t="n">
-        <v>510.9282940964621</v>
+        <v>566.1780592500394</v>
       </c>
       <c r="P22" t="n">
-        <v>175.5772469524825</v>
+        <v>230.8270121060598</v>
       </c>
       <c r="Q22" t="n">
-        <v>40.08</v>
+        <v>97.60651534814011</v>
       </c>
       <c r="R22" t="n">
-        <v>40.08</v>
+        <v>97.60651534814011</v>
       </c>
       <c r="S22" t="n">
         <v>40.08</v>
@@ -5956,19 +5956,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>194.0947254979737</v>
+        <v>624.1186386787112</v>
       </c>
       <c r="C23" t="n">
-        <v>40.08</v>
+        <v>470.1039131807375</v>
       </c>
       <c r="D23" t="n">
-        <v>40.08</v>
+        <v>355.6199174839196</v>
       </c>
       <c r="E23" t="n">
-        <v>40.08</v>
+        <v>247.1721502042543</v>
       </c>
       <c r="F23" t="n">
-        <v>40.08</v>
+        <v>138.1927272668686</v>
       </c>
       <c r="G23" t="n">
         <v>40.08</v>
@@ -5983,22 +5983,22 @@
         <v>95.91487447062691</v>
       </c>
       <c r="K23" t="n">
-        <v>231.5920561791696</v>
+        <v>580.4374448412391</v>
       </c>
       <c r="L23" t="n">
-        <v>727.5820561791696</v>
+        <v>748.7569861477718</v>
       </c>
       <c r="M23" t="n">
-        <v>1223.57205617917</v>
+        <v>1244.746986147772</v>
       </c>
       <c r="N23" t="n">
-        <v>1719.56205617917</v>
+        <v>1740.736986147772</v>
       </c>
       <c r="O23" t="n">
-        <v>1829.728967411371</v>
+        <v>1850.903897379973</v>
       </c>
       <c r="P23" t="n">
-        <v>1982.825070031398</v>
+        <v>2004</v>
       </c>
       <c r="Q23" t="n">
         <v>2004</v>
@@ -6016,16 +6016,16 @@
         <v>1185.422586823917</v>
       </c>
       <c r="V23" t="n">
-        <v>849.2094310998527</v>
+        <v>1185.422586823917</v>
       </c>
       <c r="W23" t="n">
-        <v>504.3877381898047</v>
+        <v>840.6008939138692</v>
       </c>
       <c r="X23" t="n">
-        <v>504.3877381898047</v>
+        <v>840.6008939138692</v>
       </c>
       <c r="Y23" t="n">
-        <v>287.9054829546467</v>
+        <v>624.1186386787112</v>
       </c>
     </row>
     <row r="24">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>603.8272609894487</v>
+        <v>303.8272609894487</v>
       </c>
       <c r="C24" t="n">
         <v>239.0798746808434</v>
@@ -6062,37 +6062,37 @@
         <v>217.9540496092612</v>
       </c>
       <c r="K24" t="n">
-        <v>490.3306571628144</v>
+        <v>499.300511364022</v>
       </c>
       <c r="L24" t="n">
-        <v>885.5930678146183</v>
+        <v>885.5930678146174</v>
       </c>
       <c r="M24" t="n">
-        <v>1116.273009557478</v>
+        <v>1116.273009557477</v>
       </c>
       <c r="N24" t="n">
         <v>1397.979810014102</v>
       </c>
       <c r="O24" t="n">
-        <v>1772.803526226123</v>
+        <v>1772.803526226122</v>
       </c>
       <c r="P24" t="n">
-        <v>1994.309306167328</v>
+        <v>1994.309306167327</v>
       </c>
       <c r="Q24" t="n">
-        <v>1893.808733463013</v>
+        <v>1994.309306167327</v>
       </c>
       <c r="R24" t="n">
-        <v>1677.159081157007</v>
+        <v>1777.659653861322</v>
       </c>
       <c r="S24" t="n">
-        <v>1516.69782714282</v>
+        <v>1617.198399847135</v>
       </c>
       <c r="T24" t="n">
-        <v>1409.592518270546</v>
+        <v>1510.09309097486</v>
       </c>
       <c r="U24" t="n">
-        <v>1175.235845796719</v>
+        <v>1405.878509932552</v>
       </c>
       <c r="V24" t="n">
         <v>1056.538202168921</v>
@@ -6144,25 +6144,25 @@
         <v>1195.715487565129</v>
       </c>
       <c r="L25" t="n">
-        <v>1140.465722411551</v>
+        <v>1195.715487565129</v>
       </c>
       <c r="M25" t="n">
-        <v>991.0965504367948</v>
+        <v>1195.715487565129</v>
       </c>
       <c r="N25" t="n">
-        <v>788.8437670029022</v>
+        <v>1065.338601634295</v>
       </c>
       <c r="O25" t="n">
-        <v>788.8437670029022</v>
+        <v>787.4231287278546</v>
       </c>
       <c r="P25" t="n">
-        <v>489.9007238588451</v>
+        <v>452.0720815838751</v>
       </c>
       <c r="Q25" t="n">
-        <v>97.60651534814011</v>
+        <v>452.0720815838751</v>
       </c>
       <c r="R25" t="n">
-        <v>97.60651534814011</v>
+        <v>40.08</v>
       </c>
       <c r="S25" t="n">
         <v>40.08</v>
@@ -6193,16 +6193,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>178.77656565657</v>
+        <v>510.0896969700065</v>
       </c>
       <c r="C26" t="n">
-        <v>178.77656565657</v>
+        <v>510.0896969700065</v>
       </c>
       <c r="D26" t="n">
-        <v>13.12</v>
+        <v>344.4331313133328</v>
       </c>
       <c r="E26" t="n">
-        <v>13.12</v>
+        <v>178.7765656566664</v>
       </c>
       <c r="F26" t="n">
         <v>13.12</v>
@@ -6214,55 +6214,55 @@
         <v>13.12</v>
       </c>
       <c r="I26" t="n">
-        <v>13.12</v>
+        <v>38.86492996860224</v>
       </c>
       <c r="J26" t="n">
-        <v>68.95487447062692</v>
+        <v>94.69980443922914</v>
       </c>
       <c r="K26" t="n">
-        <v>204.6320561791696</v>
+        <v>230.3769861477718</v>
       </c>
       <c r="L26" t="n">
-        <v>366.9920561791697</v>
+        <v>392.7369861477719</v>
       </c>
       <c r="M26" t="n">
-        <v>366.9920561791697</v>
+        <v>392.7369861477719</v>
       </c>
       <c r="N26" t="n">
-        <v>366.9920561791697</v>
+        <v>392.7369861477719</v>
       </c>
       <c r="O26" t="n">
-        <v>477.1589674113709</v>
+        <v>502.9038973799731</v>
       </c>
       <c r="P26" t="n">
-        <v>630.2550700313977</v>
+        <v>656</v>
       </c>
       <c r="Q26" t="n">
         <v>656</v>
       </c>
       <c r="R26" t="n">
-        <v>616.4028365726075</v>
+        <v>656</v>
       </c>
       <c r="S26" t="n">
-        <v>616.4028365726075</v>
+        <v>656</v>
       </c>
       <c r="T26" t="n">
-        <v>616.4028365726075</v>
+        <v>510.0896969700065</v>
       </c>
       <c r="U26" t="n">
-        <v>616.4028365726075</v>
+        <v>510.0896969700065</v>
       </c>
       <c r="V26" t="n">
-        <v>450.746270916038</v>
+        <v>510.0896969700065</v>
       </c>
       <c r="W26" t="n">
-        <v>450.746270916038</v>
+        <v>510.0896969700065</v>
       </c>
       <c r="X26" t="n">
-        <v>450.746270916038</v>
+        <v>510.0896969700065</v>
       </c>
       <c r="Y26" t="n">
-        <v>285.089705259468</v>
+        <v>510.0896969700065</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>66.93738997982605</v>
+        <v>344.4331313133973</v>
       </c>
       <c r="C27" t="n">
-        <v>66.93738997982605</v>
+        <v>344.4331313133973</v>
       </c>
       <c r="D27" t="n">
-        <v>66.93738997982605</v>
+        <v>344.4331313133973</v>
       </c>
       <c r="E27" t="n">
-        <v>66.93738997982605</v>
+        <v>178.7765656567235</v>
       </c>
       <c r="F27" t="n">
-        <v>66.93738997982605</v>
+        <v>178.7765656567235</v>
       </c>
       <c r="G27" t="n">
-        <v>66.93738997982605</v>
+        <v>178.7765656567235</v>
       </c>
       <c r="H27" t="n">
-        <v>66.93738997982605</v>
+        <v>13.12</v>
       </c>
       <c r="I27" t="n">
         <v>13.12</v>
       </c>
       <c r="J27" t="n">
-        <v>108.3639551007507</v>
+        <v>175.4800000000226</v>
       </c>
       <c r="K27" t="n">
-        <v>239.3489784011281</v>
+        <v>175.4800000000226</v>
       </c>
       <c r="L27" t="n">
-        <v>401.7089784011281</v>
+        <v>329.0939675566264</v>
       </c>
       <c r="M27" t="n">
-        <v>401.7089784011281</v>
+        <v>329.0939675566264</v>
       </c>
       <c r="N27" t="n">
-        <v>462.1364794785364</v>
+        <v>329.0939675566264</v>
       </c>
       <c r="O27" t="n">
-        <v>624.4964794785365</v>
+        <v>449.5806113074768</v>
       </c>
       <c r="P27" t="n">
-        <v>629.0430546975973</v>
+        <v>611.9406113074994</v>
       </c>
       <c r="Q27" t="n">
         <v>656</v>
       </c>
       <c r="R27" t="n">
-        <v>490.3434343434241</v>
+        <v>656</v>
       </c>
       <c r="S27" t="n">
-        <v>398.2505212929774</v>
+        <v>656</v>
       </c>
       <c r="T27" t="n">
-        <v>232.5939556364017</v>
+        <v>656</v>
       </c>
       <c r="U27" t="n">
-        <v>66.93738997982605</v>
+        <v>510.0896969700711</v>
       </c>
       <c r="V27" t="n">
-        <v>66.93738997982605</v>
+        <v>510.0896969700711</v>
       </c>
       <c r="W27" t="n">
-        <v>66.93738997982605</v>
+        <v>510.0896969700711</v>
       </c>
       <c r="X27" t="n">
-        <v>66.93738997982605</v>
+        <v>510.0896969700711</v>
       </c>
       <c r="Y27" t="n">
-        <v>66.93738997982605</v>
+        <v>510.0896969700711</v>
       </c>
     </row>
     <row r="28">
@@ -6351,25 +6351,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>94.40721132966942</v>
+        <v>31.40277517514846</v>
       </c>
       <c r="C28" t="n">
-        <v>94.40721132966942</v>
+        <v>31.40277517514846</v>
       </c>
       <c r="D28" t="n">
-        <v>94.40721132966942</v>
+        <v>31.40277517514846</v>
       </c>
       <c r="E28" t="n">
-        <v>94.40721132966942</v>
+        <v>31.40277517514846</v>
       </c>
       <c r="F28" t="n">
-        <v>94.40721132966942</v>
+        <v>31.40277517514846</v>
       </c>
       <c r="G28" t="n">
-        <v>94.40721132966942</v>
+        <v>31.40277517514846</v>
       </c>
       <c r="H28" t="n">
-        <v>13.12</v>
+        <v>31.40277517514846</v>
       </c>
       <c r="I28" t="n">
         <v>13.12</v>
@@ -6405,22 +6405,22 @@
         <v>154.589865898353</v>
       </c>
       <c r="T28" t="n">
-        <v>101.4092624596899</v>
+        <v>89.98416036959456</v>
       </c>
       <c r="U28" t="n">
-        <v>94.40721132966942</v>
+        <v>89.98416036959456</v>
       </c>
       <c r="V28" t="n">
-        <v>94.40721132966942</v>
+        <v>89.98416036959456</v>
       </c>
       <c r="W28" t="n">
-        <v>94.40721132966942</v>
+        <v>31.40277517514846</v>
       </c>
       <c r="X28" t="n">
-        <v>94.40721132966942</v>
+        <v>31.40277517514846</v>
       </c>
       <c r="Y28" t="n">
-        <v>94.40721132966942</v>
+        <v>31.40277517514846</v>
       </c>
     </row>
     <row r="29">
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>324.4836446533911</v>
+        <v>344.4331313134849</v>
       </c>
       <c r="C29" t="n">
-        <v>324.4836446533911</v>
+        <v>344.4331313134849</v>
       </c>
       <c r="D29" t="n">
-        <v>324.4836446533911</v>
+        <v>178.7765656567771</v>
       </c>
       <c r="E29" t="n">
-        <v>324.4836446533911</v>
+        <v>178.7765656567771</v>
       </c>
       <c r="F29" t="n">
-        <v>158.8270789968191</v>
+        <v>178.7765656567771</v>
       </c>
       <c r="G29" t="n">
         <v>13.12</v>
@@ -6451,28 +6451,28 @@
         <v>13.12</v>
       </c>
       <c r="I29" t="n">
-        <v>15.19293515824415</v>
+        <v>15.1929351582438</v>
       </c>
       <c r="J29" t="n">
-        <v>71.02780962887107</v>
+        <v>71.02780962887071</v>
       </c>
       <c r="K29" t="n">
-        <v>206.7049913374138</v>
+        <v>206.7049913374134</v>
       </c>
       <c r="L29" t="n">
-        <v>369.0649913374138</v>
+        <v>369.0649913374134</v>
       </c>
       <c r="M29" t="n">
-        <v>392.7369861477719</v>
+        <v>369.0649913374134</v>
       </c>
       <c r="N29" t="n">
-        <v>392.7369861477719</v>
+        <v>369.0649913374134</v>
       </c>
       <c r="O29" t="n">
-        <v>502.9038973799731</v>
+        <v>479.2319025696146</v>
       </c>
       <c r="P29" t="n">
-        <v>656</v>
+        <v>632.3280051896415</v>
       </c>
       <c r="Q29" t="n">
         <v>656</v>
@@ -6487,19 +6487,19 @@
         <v>655.7967759665469</v>
       </c>
       <c r="U29" t="n">
-        <v>490.1402103099666</v>
+        <v>655.7967759665469</v>
       </c>
       <c r="V29" t="n">
-        <v>324.4836446533911</v>
+        <v>655.7967759665469</v>
       </c>
       <c r="W29" t="n">
-        <v>324.4836446533911</v>
+        <v>490.1402103098393</v>
       </c>
       <c r="X29" t="n">
-        <v>324.4836446533911</v>
+        <v>490.1402103098393</v>
       </c>
       <c r="Y29" t="n">
-        <v>324.4836446533911</v>
+        <v>344.4331313134849</v>
       </c>
     </row>
     <row r="30">
@@ -6509,46 +6509,46 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>329.360950972468</v>
+        <v>324.6868686865139</v>
       </c>
       <c r="C30" t="n">
-        <v>329.360950972468</v>
+        <v>159.0303030298062</v>
       </c>
       <c r="D30" t="n">
-        <v>329.360950972468</v>
+        <v>159.0303030298062</v>
       </c>
       <c r="E30" t="n">
-        <v>329.360950972468</v>
+        <v>159.0303030298062</v>
       </c>
       <c r="F30" t="n">
-        <v>171.142524368552</v>
+        <v>13.12</v>
       </c>
       <c r="G30" t="n">
-        <v>27.54345058588665</v>
+        <v>13.12</v>
       </c>
       <c r="H30" t="n">
-        <v>27.54345058588665</v>
+        <v>13.12</v>
       </c>
       <c r="I30" t="n">
         <v>13.12</v>
       </c>
       <c r="J30" t="n">
-        <v>175.48</v>
+        <v>168.9199999999702</v>
       </c>
       <c r="K30" t="n">
-        <v>315.6794572243354</v>
+        <v>168.9199999999702</v>
       </c>
       <c r="L30" t="n">
-        <v>326.7334247809391</v>
+        <v>331.2799999999702</v>
       </c>
       <c r="M30" t="n">
-        <v>489.0934247809391</v>
+        <v>331.2799999999702</v>
       </c>
       <c r="N30" t="n">
-        <v>489.0934247809391</v>
+        <v>493.6399999999702</v>
       </c>
       <c r="O30" t="n">
-        <v>651.4534247809391</v>
+        <v>493.6399999999702</v>
       </c>
       <c r="P30" t="n">
         <v>656</v>
@@ -6563,22 +6563,22 @@
         <v>656</v>
       </c>
       <c r="T30" t="n">
-        <v>656</v>
+        <v>490.3434343432218</v>
       </c>
       <c r="U30" t="n">
-        <v>656</v>
+        <v>490.3434343432218</v>
       </c>
       <c r="V30" t="n">
-        <v>656</v>
+        <v>490.3434343432218</v>
       </c>
       <c r="W30" t="n">
-        <v>656</v>
+        <v>490.3434343432218</v>
       </c>
       <c r="X30" t="n">
-        <v>495.0175166290446</v>
+        <v>490.3434343432218</v>
       </c>
       <c r="Y30" t="n">
-        <v>495.0175166290446</v>
+        <v>490.3434343432218</v>
       </c>
     </row>
     <row r="31">
@@ -6618,37 +6618,37 @@
         <v>196.171052050837</v>
       </c>
       <c r="L31" t="n">
-        <v>196.171052050837</v>
+        <v>188.9225479050453</v>
       </c>
       <c r="M31" t="n">
-        <v>196.171052050837</v>
+        <v>188.9225479050453</v>
       </c>
       <c r="N31" t="n">
-        <v>196.171052050837</v>
+        <v>188.9225479050453</v>
       </c>
       <c r="O31" t="n">
-        <v>196.171052050837</v>
+        <v>188.9225479050453</v>
       </c>
       <c r="P31" t="n">
-        <v>196.171052050837</v>
+        <v>188.9225479050453</v>
       </c>
       <c r="Q31" t="n">
-        <v>196.171052050837</v>
+        <v>188.9225479050453</v>
       </c>
       <c r="R31" t="n">
-        <v>196.171052050837</v>
+        <v>188.9225479050453</v>
       </c>
       <c r="S31" t="n">
-        <v>108.6223140951284</v>
+        <v>23.26598224826305</v>
       </c>
       <c r="T31" t="n">
-        <v>83.4105479603094</v>
+        <v>23.26598224826305</v>
       </c>
       <c r="U31" t="n">
-        <v>115.1578376477764</v>
+        <v>55.01327193573002</v>
       </c>
       <c r="V31" t="n">
-        <v>98.82419096472969</v>
+        <v>55.01327193573002</v>
       </c>
       <c r="W31" t="n">
         <v>55.01327193573002</v>
@@ -6667,40 +6667,40 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>490.1402103099696</v>
+        <v>178.7765656566034</v>
       </c>
       <c r="C32" t="n">
-        <v>344.4331313131557</v>
+        <v>178.7765656566034</v>
       </c>
       <c r="D32" t="n">
-        <v>344.4331313131557</v>
+        <v>178.7765656566034</v>
       </c>
       <c r="E32" t="n">
-        <v>178.7765656565801</v>
+        <v>13.12</v>
       </c>
       <c r="F32" t="n">
-        <v>178.7765656565801</v>
+        <v>13.12</v>
       </c>
       <c r="G32" t="n">
-        <v>178.7765656565801</v>
+        <v>13.12</v>
       </c>
       <c r="H32" t="n">
         <v>13.12</v>
       </c>
       <c r="I32" t="n">
-        <v>13.12</v>
+        <v>15.19293515824434</v>
       </c>
       <c r="J32" t="n">
-        <v>68.95487447062692</v>
+        <v>94.69980443922914</v>
       </c>
       <c r="K32" t="n">
-        <v>204.6320561791696</v>
+        <v>230.3769861477718</v>
       </c>
       <c r="L32" t="n">
-        <v>366.9920561791697</v>
+        <v>392.7369861477719</v>
       </c>
       <c r="M32" t="n">
-        <v>366.9920561791697</v>
+        <v>392.7369861477719</v>
       </c>
       <c r="N32" t="n">
         <v>392.7369861477719</v>
@@ -6724,19 +6724,19 @@
         <v>655.7967759665469</v>
       </c>
       <c r="U32" t="n">
-        <v>655.7967759665469</v>
+        <v>510.0896969698102</v>
       </c>
       <c r="V32" t="n">
-        <v>655.7967759665469</v>
+        <v>510.0896969698102</v>
       </c>
       <c r="W32" t="n">
-        <v>655.7967759665469</v>
+        <v>510.0896969698102</v>
       </c>
       <c r="X32" t="n">
-        <v>655.7967759665469</v>
+        <v>344.4331313132068</v>
       </c>
       <c r="Y32" t="n">
-        <v>655.7967759665469</v>
+        <v>344.4331313132068</v>
       </c>
     </row>
     <row r="33">
@@ -6746,46 +6746,46 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>324.6868686868361</v>
+        <v>178.7765656567298</v>
       </c>
       <c r="C33" t="n">
-        <v>159.0303030302582</v>
+        <v>178.7765656567298</v>
       </c>
       <c r="D33" t="n">
-        <v>159.0303030302582</v>
+        <v>13.12</v>
       </c>
       <c r="E33" t="n">
-        <v>159.0303030302582</v>
+        <v>13.12</v>
       </c>
       <c r="F33" t="n">
-        <v>159.0303030302582</v>
+        <v>13.12</v>
       </c>
       <c r="G33" t="n">
-        <v>159.0303030302582</v>
+        <v>13.12</v>
       </c>
       <c r="H33" t="n">
-        <v>27.54345058588665</v>
+        <v>13.12</v>
       </c>
       <c r="I33" t="n">
         <v>13.12</v>
       </c>
       <c r="J33" t="n">
-        <v>13.12</v>
+        <v>175.480000000037</v>
       </c>
       <c r="K33" t="n">
-        <v>13.12</v>
+        <v>315.6794572243354</v>
       </c>
       <c r="L33" t="n">
-        <v>168.92</v>
+        <v>326.7334247809391</v>
       </c>
       <c r="M33" t="n">
-        <v>331.28</v>
+        <v>326.7334247809391</v>
       </c>
       <c r="N33" t="n">
-        <v>493.64</v>
+        <v>489.0934247809391</v>
       </c>
       <c r="O33" t="n">
-        <v>493.64</v>
+        <v>651.4534247809391</v>
       </c>
       <c r="P33" t="n">
         <v>656</v>
@@ -6794,28 +6794,28 @@
         <v>656</v>
       </c>
       <c r="R33" t="n">
-        <v>490.3434343434188</v>
+        <v>656</v>
       </c>
       <c r="S33" t="n">
-        <v>490.3434343434188</v>
+        <v>656</v>
       </c>
       <c r="T33" t="n">
-        <v>324.6868686868361</v>
+        <v>510.089696970189</v>
       </c>
       <c r="U33" t="n">
-        <v>324.6868686868361</v>
+        <v>510.089696970189</v>
       </c>
       <c r="V33" t="n">
-        <v>324.6868686868361</v>
+        <v>344.4331313134594</v>
       </c>
       <c r="W33" t="n">
-        <v>324.6868686868361</v>
+        <v>344.4331313134594</v>
       </c>
       <c r="X33" t="n">
-        <v>324.6868686868361</v>
+        <v>178.7765656567298</v>
       </c>
       <c r="Y33" t="n">
-        <v>324.6868686868361</v>
+        <v>178.7765656567298</v>
       </c>
     </row>
     <row r="34">
@@ -6825,22 +6825,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>142.5620098914386</v>
+        <v>13.12</v>
       </c>
       <c r="C34" t="n">
-        <v>142.5620098914386</v>
+        <v>13.12</v>
       </c>
       <c r="D34" t="n">
-        <v>142.5620098914386</v>
+        <v>13.12</v>
       </c>
       <c r="E34" t="n">
-        <v>142.5620098914386</v>
+        <v>13.12</v>
       </c>
       <c r="F34" t="n">
-        <v>117.1956902720992</v>
+        <v>13.12</v>
       </c>
       <c r="G34" t="n">
-        <v>55.01327193573003</v>
+        <v>13.12</v>
       </c>
       <c r="H34" t="n">
         <v>13.12</v>
@@ -6864,37 +6864,37 @@
         <v>196.171052050837</v>
       </c>
       <c r="O34" t="n">
-        <v>196.171052050837</v>
+        <v>102.8718118815177</v>
       </c>
       <c r="P34" t="n">
-        <v>196.171052050837</v>
+        <v>102.8718118815177</v>
       </c>
       <c r="Q34" t="n">
-        <v>196.171052050837</v>
+        <v>102.8718118815177</v>
       </c>
       <c r="R34" t="n">
-        <v>196.171052050837</v>
+        <v>102.8718118815177</v>
       </c>
       <c r="S34" t="n">
-        <v>196.171052050837</v>
+        <v>102.8718118815177</v>
       </c>
       <c r="T34" t="n">
-        <v>170.959285916018</v>
+        <v>102.8718118815177</v>
       </c>
       <c r="U34" t="n">
-        <v>202.7065756034849</v>
+        <v>134.6191015689847</v>
       </c>
       <c r="V34" t="n">
-        <v>186.3729289204383</v>
+        <v>118.2854548859381</v>
       </c>
       <c r="W34" t="n">
-        <v>142.5620098914386</v>
+        <v>118.2854548859381</v>
       </c>
       <c r="X34" t="n">
-        <v>142.5620098914386</v>
+        <v>118.2854548859381</v>
       </c>
       <c r="Y34" t="n">
-        <v>142.5620098914386</v>
+        <v>118.2854548859381</v>
       </c>
     </row>
     <row r="35">
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>490.1402103099695</v>
+        <v>324.4836446533253</v>
       </c>
       <c r="C35" t="n">
-        <v>324.4836446533911</v>
+        <v>324.4836446533253</v>
       </c>
       <c r="D35" t="n">
-        <v>324.4836446533911</v>
+        <v>158.8270789967145</v>
       </c>
       <c r="E35" t="n">
-        <v>324.4836446533911</v>
+        <v>158.8270789967145</v>
       </c>
       <c r="F35" t="n">
-        <v>324.4836446533911</v>
+        <v>13.12</v>
       </c>
       <c r="G35" t="n">
-        <v>158.8270789968091</v>
+        <v>13.12</v>
       </c>
       <c r="H35" t="n">
         <v>13.12</v>
@@ -6937,7 +6937,7 @@
         <v>366.9920561791697</v>
       </c>
       <c r="M35" t="n">
-        <v>392.7369861477719</v>
+        <v>366.9920561791697</v>
       </c>
       <c r="N35" t="n">
         <v>392.7369861477719</v>
@@ -6955,25 +6955,25 @@
         <v>655.7967759665469</v>
       </c>
       <c r="S35" t="n">
-        <v>655.7967759665469</v>
+        <v>490.1402103099361</v>
       </c>
       <c r="T35" t="n">
-        <v>655.7967759665469</v>
+        <v>490.1402103099361</v>
       </c>
       <c r="U35" t="n">
-        <v>655.7967759665469</v>
+        <v>324.4836446533253</v>
       </c>
       <c r="V35" t="n">
-        <v>655.7967759665469</v>
+        <v>324.4836446533253</v>
       </c>
       <c r="W35" t="n">
-        <v>655.7967759665469</v>
+        <v>324.4836446533253</v>
       </c>
       <c r="X35" t="n">
-        <v>655.7967759665469</v>
+        <v>324.4836446533253</v>
       </c>
       <c r="Y35" t="n">
-        <v>490.1402103099695</v>
+        <v>324.4836446533253</v>
       </c>
     </row>
     <row r="36">
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>171.142524368552</v>
+        <v>324.6868686862992</v>
       </c>
       <c r="C36" t="n">
-        <v>171.142524368552</v>
+        <v>159.0303030295217</v>
       </c>
       <c r="D36" t="n">
-        <v>171.142524368552</v>
+        <v>159.0303030295217</v>
       </c>
       <c r="E36" t="n">
-        <v>171.142524368552</v>
+        <v>13.12</v>
       </c>
       <c r="F36" t="n">
-        <v>171.142524368552</v>
+        <v>13.12</v>
       </c>
       <c r="G36" t="n">
-        <v>27.54345058588665</v>
+        <v>13.12</v>
       </c>
       <c r="H36" t="n">
-        <v>27.54345058588665</v>
+        <v>13.12</v>
       </c>
       <c r="I36" t="n">
         <v>13.12</v>
@@ -7013,46 +7013,46 @@
         <v>175.48</v>
       </c>
       <c r="L36" t="n">
-        <v>186.5339675566038</v>
+        <v>326.7334247809391</v>
       </c>
       <c r="M36" t="n">
-        <v>348.8939675566038</v>
+        <v>489.0934247809391</v>
       </c>
       <c r="N36" t="n">
-        <v>511.2539675566038</v>
+        <v>651.4534247809391</v>
       </c>
       <c r="O36" t="n">
-        <v>647.561782361217</v>
+        <v>651.4534247809391</v>
       </c>
       <c r="P36" t="n">
-        <v>652.1083575802778</v>
+        <v>656</v>
       </c>
       <c r="Q36" t="n">
         <v>656</v>
       </c>
       <c r="R36" t="n">
-        <v>502.4556556817074</v>
+        <v>656</v>
       </c>
       <c r="S36" t="n">
-        <v>502.4556556817074</v>
+        <v>656</v>
       </c>
       <c r="T36" t="n">
-        <v>502.4556556817074</v>
+        <v>656</v>
       </c>
       <c r="U36" t="n">
-        <v>502.4556556817074</v>
+        <v>490.3434343430767</v>
       </c>
       <c r="V36" t="n">
-        <v>336.7990900251287</v>
+        <v>324.6868686862992</v>
       </c>
       <c r="W36" t="n">
-        <v>336.7990900251287</v>
+        <v>324.6868686862992</v>
       </c>
       <c r="X36" t="n">
-        <v>171.142524368552</v>
+        <v>324.6868686862992</v>
       </c>
       <c r="Y36" t="n">
-        <v>171.142524368552</v>
+        <v>324.6868686862992</v>
       </c>
     </row>
     <row r="37">
@@ -7062,22 +7062,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>186.3729289204383</v>
+        <v>13.12</v>
       </c>
       <c r="C37" t="n">
-        <v>186.3729289204383</v>
+        <v>13.12</v>
       </c>
       <c r="D37" t="n">
-        <v>186.3729289204383</v>
+        <v>13.12</v>
       </c>
       <c r="E37" t="n">
-        <v>147.3191870546613</v>
+        <v>13.12</v>
       </c>
       <c r="F37" t="n">
-        <v>55.01327193573002</v>
+        <v>13.12</v>
       </c>
       <c r="G37" t="n">
-        <v>55.01327193573002</v>
+        <v>13.12</v>
       </c>
       <c r="H37" t="n">
         <v>13.12</v>
@@ -7101,37 +7101,37 @@
         <v>196.171052050837</v>
       </c>
       <c r="O37" t="n">
-        <v>196.171052050837</v>
+        <v>30.51448639427133</v>
       </c>
       <c r="P37" t="n">
-        <v>196.171052050837</v>
+        <v>30.51448639427133</v>
       </c>
       <c r="Q37" t="n">
-        <v>196.171052050837</v>
+        <v>30.51448639427133</v>
       </c>
       <c r="R37" t="n">
-        <v>196.171052050837</v>
+        <v>30.51448639427133</v>
       </c>
       <c r="S37" t="n">
-        <v>196.171052050837</v>
+        <v>30.51448639427133</v>
       </c>
       <c r="T37" t="n">
-        <v>170.959285916018</v>
+        <v>30.51448639427133</v>
       </c>
       <c r="U37" t="n">
-        <v>202.706575603485</v>
+        <v>62.2617760817383</v>
       </c>
       <c r="V37" t="n">
-        <v>186.3729289204383</v>
+        <v>62.2617760817383</v>
       </c>
       <c r="W37" t="n">
-        <v>186.3729289204383</v>
+        <v>62.2617760817383</v>
       </c>
       <c r="X37" t="n">
-        <v>186.3729289204383</v>
+        <v>62.2617760817383</v>
       </c>
       <c r="Y37" t="n">
-        <v>186.3729289204383</v>
+        <v>62.2617760817383</v>
       </c>
     </row>
     <row r="38">
@@ -7141,16 +7141,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>13.12</v>
+        <v>344.4331313136288</v>
       </c>
       <c r="C38" t="n">
-        <v>13.12</v>
+        <v>344.4331313136288</v>
       </c>
       <c r="D38" t="n">
-        <v>13.12</v>
+        <v>178.7765656568071</v>
       </c>
       <c r="E38" t="n">
-        <v>13.12</v>
+        <v>178.7765656568071</v>
       </c>
       <c r="F38" t="n">
         <v>13.12</v>
@@ -7174,16 +7174,16 @@
         <v>366.9920561791697</v>
       </c>
       <c r="M38" t="n">
-        <v>366.9920561791697</v>
+        <v>383.4730887677474</v>
       </c>
       <c r="N38" t="n">
-        <v>366.9920561791697</v>
+        <v>383.4730887677474</v>
       </c>
       <c r="O38" t="n">
-        <v>477.1589674113709</v>
+        <v>493.6399999999486</v>
       </c>
       <c r="P38" t="n">
-        <v>630.2550700313977</v>
+        <v>656</v>
       </c>
       <c r="Q38" t="n">
         <v>656</v>
@@ -7198,19 +7198,19 @@
         <v>655.7967759665469</v>
       </c>
       <c r="U38" t="n">
-        <v>490.140210309963</v>
+        <v>510.0896969704503</v>
       </c>
       <c r="V38" t="n">
-        <v>324.4836446533828</v>
+        <v>510.0896969704503</v>
       </c>
       <c r="W38" t="n">
-        <v>158.8270789968037</v>
+        <v>344.4331313136288</v>
       </c>
       <c r="X38" t="n">
-        <v>13.12</v>
+        <v>344.4331313136288</v>
       </c>
       <c r="Y38" t="n">
-        <v>13.12</v>
+        <v>344.4331313136288</v>
       </c>
     </row>
     <row r="39">
@@ -7220,37 +7220,37 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>477.4787502812962</v>
+        <v>324.686868686357</v>
       </c>
       <c r="C39" t="n">
-        <v>477.4787502812962</v>
+        <v>324.686868686357</v>
       </c>
       <c r="D39" t="n">
-        <v>477.4787502812962</v>
+        <v>171.338426603916</v>
       </c>
       <c r="E39" t="n">
-        <v>316.1938035924956</v>
+        <v>171.338426603916</v>
       </c>
       <c r="F39" t="n">
-        <v>316.1938035924956</v>
+        <v>13.12</v>
       </c>
       <c r="G39" t="n">
-        <v>172.5947298098302</v>
+        <v>13.12</v>
       </c>
       <c r="H39" t="n">
-        <v>27.54345058588665</v>
+        <v>13.12</v>
       </c>
       <c r="I39" t="n">
         <v>13.12</v>
       </c>
       <c r="J39" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="K39" t="n">
         <v>175.48</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>337.84</v>
-      </c>
-      <c r="L39" t="n">
-        <v>500.1999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>500.1999999999999</v>
@@ -7262,7 +7262,7 @@
         <v>500.1999999999999</v>
       </c>
       <c r="P39" t="n">
-        <v>656</v>
+        <v>652.1083575802772</v>
       </c>
       <c r="Q39" t="n">
         <v>656</v>
@@ -7280,16 +7280,16 @@
         <v>656</v>
       </c>
       <c r="V39" t="n">
-        <v>490.34343434342</v>
+        <v>490.3434343431785</v>
       </c>
       <c r="W39" t="n">
-        <v>477.4787502812962</v>
+        <v>490.3434343431785</v>
       </c>
       <c r="X39" t="n">
-        <v>477.4787502812962</v>
+        <v>324.686868686357</v>
       </c>
       <c r="Y39" t="n">
-        <v>477.4787502812962</v>
+        <v>324.686868686357</v>
       </c>
     </row>
     <row r="40">
@@ -7335,31 +7335,31 @@
         <v>196.171052050837</v>
       </c>
       <c r="N40" t="n">
-        <v>196.171052050837</v>
+        <v>30.51448639383162</v>
       </c>
       <c r="O40" t="n">
-        <v>196.171052050837</v>
+        <v>30.51448639383162</v>
       </c>
       <c r="P40" t="n">
-        <v>196.171052050837</v>
+        <v>30.51448639383162</v>
       </c>
       <c r="Q40" t="n">
-        <v>108.6223140951284</v>
+        <v>30.51448639383162</v>
       </c>
       <c r="R40" t="n">
-        <v>108.6223140951284</v>
+        <v>30.51448639383162</v>
       </c>
       <c r="S40" t="n">
-        <v>108.6223140951284</v>
+        <v>23.26598224826306</v>
       </c>
       <c r="T40" t="n">
-        <v>83.41054796030943</v>
+        <v>23.26598224826306</v>
       </c>
       <c r="U40" t="n">
-        <v>115.1578376477764</v>
+        <v>55.01327193573003</v>
       </c>
       <c r="V40" t="n">
-        <v>98.82419096472972</v>
+        <v>55.01327193573003</v>
       </c>
       <c r="W40" t="n">
         <v>55.01327193573003</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>178.7765656565714</v>
+        <v>490.3434343431571</v>
       </c>
       <c r="C41" t="n">
-        <v>178.7765656565714</v>
+        <v>490.3434343431571</v>
       </c>
       <c r="D41" t="n">
-        <v>178.7765656565714</v>
+        <v>324.6868686863141</v>
       </c>
       <c r="E41" t="n">
-        <v>178.7765656565714</v>
+        <v>324.6868686863141</v>
       </c>
       <c r="F41" t="n">
-        <v>13.12</v>
+        <v>324.6868686863141</v>
       </c>
       <c r="G41" t="n">
-        <v>13.12</v>
+        <v>159.0303030292979</v>
       </c>
       <c r="H41" t="n">
         <v>13.12</v>
@@ -7405,49 +7405,49 @@
         <v>68.95487447062692</v>
       </c>
       <c r="K41" t="n">
-        <v>204.6320561791696</v>
+        <v>230.3769861477718</v>
       </c>
       <c r="L41" t="n">
-        <v>366.9920561791697</v>
+        <v>392.7369861477719</v>
       </c>
       <c r="M41" t="n">
-        <v>366.9920561791697</v>
+        <v>392.7369861477719</v>
       </c>
       <c r="N41" t="n">
-        <v>366.9920561791697</v>
+        <v>392.7369861477719</v>
       </c>
       <c r="O41" t="n">
-        <v>477.1589674113709</v>
+        <v>502.9038973799731</v>
       </c>
       <c r="P41" t="n">
-        <v>630.2550700313977</v>
+        <v>656</v>
       </c>
       <c r="Q41" t="n">
         <v>656</v>
       </c>
       <c r="R41" t="n">
-        <v>592.1604123301832</v>
+        <v>656</v>
       </c>
       <c r="S41" t="n">
-        <v>592.1604123301832</v>
+        <v>656</v>
       </c>
       <c r="T41" t="n">
-        <v>426.5038466736064</v>
+        <v>656</v>
       </c>
       <c r="U41" t="n">
-        <v>426.5038466736064</v>
+        <v>656</v>
       </c>
       <c r="V41" t="n">
-        <v>426.5038466736064</v>
+        <v>656</v>
       </c>
       <c r="W41" t="n">
-        <v>426.5038466736064</v>
+        <v>490.3434343431571</v>
       </c>
       <c r="X41" t="n">
-        <v>260.8472810170351</v>
+        <v>490.3434343431571</v>
       </c>
       <c r="Y41" t="n">
-        <v>260.8472810170351</v>
+        <v>490.3434343431571</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>159.0303030302807</v>
+        <v>344.4331313138535</v>
       </c>
       <c r="C42" t="n">
-        <v>159.0303030302807</v>
+        <v>344.4331313138535</v>
       </c>
       <c r="D42" t="n">
-        <v>91.17981422225029</v>
+        <v>344.4331313138535</v>
       </c>
       <c r="E42" t="n">
-        <v>91.17981422225029</v>
+        <v>178.7765656570251</v>
       </c>
       <c r="F42" t="n">
-        <v>91.17981422225029</v>
+        <v>178.7765656570251</v>
       </c>
       <c r="G42" t="n">
-        <v>91.17981422225029</v>
+        <v>178.7765656570251</v>
       </c>
       <c r="H42" t="n">
-        <v>91.17981422225029</v>
+        <v>13.12</v>
       </c>
       <c r="I42" t="n">
         <v>13.12</v>
@@ -7484,22 +7484,22 @@
         <v>13.12</v>
       </c>
       <c r="K42" t="n">
-        <v>175.48</v>
+        <v>78.07945722433541</v>
       </c>
       <c r="L42" t="n">
-        <v>305.3339675566037</v>
+        <v>207.9334247809392</v>
       </c>
       <c r="M42" t="n">
-        <v>414.6877440794103</v>
+        <v>370.2934247809392</v>
       </c>
       <c r="N42" t="n">
-        <v>414.6877440794103</v>
+        <v>370.2934247809392</v>
       </c>
       <c r="O42" t="n">
-        <v>529.4564794785365</v>
+        <v>532.6534247809392</v>
       </c>
       <c r="P42" t="n">
-        <v>652.8030546975973</v>
+        <v>656</v>
       </c>
       <c r="Q42" t="n">
         <v>656</v>
@@ -7508,25 +7508,25 @@
         <v>656</v>
       </c>
       <c r="S42" t="n">
-        <v>490.343434343424</v>
+        <v>656</v>
       </c>
       <c r="T42" t="n">
-        <v>490.343434343424</v>
+        <v>490.3434343429811</v>
       </c>
       <c r="U42" t="n">
-        <v>490.343434343424</v>
+        <v>490.3434343429811</v>
       </c>
       <c r="V42" t="n">
-        <v>324.6868686868519</v>
+        <v>490.3434343429811</v>
       </c>
       <c r="W42" t="n">
-        <v>324.6868686868519</v>
+        <v>490.3434343429811</v>
       </c>
       <c r="X42" t="n">
-        <v>159.0303030302807</v>
+        <v>344.4331313138535</v>
       </c>
       <c r="Y42" t="n">
-        <v>159.0303030302807</v>
+        <v>344.4331313138535</v>
       </c>
     </row>
     <row r="43">
@@ -7536,19 +7536,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>99.58539052590827</v>
+        <v>13.12</v>
       </c>
       <c r="C43" t="n">
-        <v>99.58539052590827</v>
+        <v>13.12</v>
       </c>
       <c r="D43" t="n">
-        <v>99.58539052590827</v>
+        <v>13.12</v>
       </c>
       <c r="E43" t="n">
-        <v>99.58539052590827</v>
+        <v>13.12</v>
       </c>
       <c r="F43" t="n">
-        <v>99.58539052590827</v>
+        <v>13.12</v>
       </c>
       <c r="G43" t="n">
         <v>13.12</v>
@@ -7581,31 +7581,31 @@
         <v>130.8298658983529</v>
       </c>
       <c r="Q43" t="n">
-        <v>130.8298658983529</v>
+        <v>13.12</v>
       </c>
       <c r="R43" t="n">
-        <v>130.8298658983529</v>
+        <v>13.12</v>
       </c>
       <c r="S43" t="n">
-        <v>130.8298658983529</v>
+        <v>13.12</v>
       </c>
       <c r="T43" t="n">
-        <v>130.8298658983529</v>
+        <v>13.12</v>
       </c>
       <c r="U43" t="n">
-        <v>99.58539052590827</v>
+        <v>13.12</v>
       </c>
       <c r="V43" t="n">
-        <v>99.58539052590827</v>
+        <v>13.12</v>
       </c>
       <c r="W43" t="n">
-        <v>99.58539052590827</v>
+        <v>13.12</v>
       </c>
       <c r="X43" t="n">
-        <v>99.58539052590827</v>
+        <v>13.12</v>
       </c>
       <c r="Y43" t="n">
-        <v>99.58539052590827</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>507.3119274816984</v>
+        <v>656</v>
       </c>
       <c r="C44" t="n">
-        <v>507.3119274816984</v>
+        <v>490.3434343432315</v>
       </c>
       <c r="D44" t="n">
-        <v>507.3119274816984</v>
+        <v>490.3434343432315</v>
       </c>
       <c r="E44" t="n">
-        <v>507.3119274816984</v>
+        <v>490.3434343432315</v>
       </c>
       <c r="F44" t="n">
-        <v>341.655361825128</v>
+        <v>324.686868686463</v>
       </c>
       <c r="G44" t="n">
-        <v>175.9987961685566</v>
+        <v>159.0303030296435</v>
       </c>
       <c r="H44" t="n">
         <v>13.12</v>
@@ -7642,49 +7642,49 @@
         <v>68.95487447062692</v>
       </c>
       <c r="K44" t="n">
-        <v>204.6320561791696</v>
+        <v>230.3769861477718</v>
       </c>
       <c r="L44" t="n">
-        <v>366.9920561791697</v>
+        <v>392.7369861477719</v>
       </c>
       <c r="M44" t="n">
-        <v>366.9920561791697</v>
+        <v>392.7369861477719</v>
       </c>
       <c r="N44" t="n">
-        <v>366.9920561791697</v>
+        <v>392.7369861477719</v>
       </c>
       <c r="O44" t="n">
-        <v>477.1589674113709</v>
+        <v>502.9038973799731</v>
       </c>
       <c r="P44" t="n">
-        <v>630.2550700313977</v>
+        <v>656</v>
       </c>
       <c r="Q44" t="n">
         <v>656</v>
       </c>
       <c r="R44" t="n">
-        <v>507.3119274816984</v>
+        <v>656</v>
       </c>
       <c r="S44" t="n">
-        <v>507.3119274816984</v>
+        <v>656</v>
       </c>
       <c r="T44" t="n">
-        <v>507.3119274816984</v>
+        <v>656</v>
       </c>
       <c r="U44" t="n">
-        <v>507.3119274816984</v>
+        <v>656</v>
       </c>
       <c r="V44" t="n">
-        <v>507.3119274816984</v>
+        <v>656</v>
       </c>
       <c r="W44" t="n">
-        <v>507.3119274816984</v>
+        <v>656</v>
       </c>
       <c r="X44" t="n">
-        <v>507.3119274816984</v>
+        <v>656</v>
       </c>
       <c r="Y44" t="n">
-        <v>507.3119274816984</v>
+        <v>656</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>341.6848647273051</v>
+        <v>324.6868686864484</v>
       </c>
       <c r="C45" t="n">
-        <v>341.6848647273051</v>
+        <v>178.7765656568538</v>
       </c>
       <c r="D45" t="n">
-        <v>341.6848647273051</v>
+        <v>178.7765656568538</v>
       </c>
       <c r="E45" t="n">
-        <v>341.6848647273051</v>
+        <v>178.7765656568538</v>
       </c>
       <c r="F45" t="n">
-        <v>341.6848647273051</v>
+        <v>178.7765656568538</v>
       </c>
       <c r="G45" t="n">
-        <v>341.6848647273051</v>
+        <v>13.12</v>
       </c>
       <c r="H45" t="n">
-        <v>176.0282990707351</v>
+        <v>13.12</v>
       </c>
       <c r="I45" t="n">
         <v>13.12</v>
       </c>
       <c r="J45" t="n">
-        <v>13.12</v>
+        <v>175.480000000073</v>
       </c>
       <c r="K45" t="n">
-        <v>82.03945722433537</v>
+        <v>175.480000000073</v>
       </c>
       <c r="L45" t="n">
-        <v>128.7334247809391</v>
+        <v>186.5339675566768</v>
       </c>
       <c r="M45" t="n">
-        <v>291.0934247809391</v>
+        <v>331.279999999927</v>
       </c>
       <c r="N45" t="n">
-        <v>453.4534247809391</v>
+        <v>493.639999999927</v>
       </c>
       <c r="O45" t="n">
-        <v>615.8134247809392</v>
+        <v>493.639999999927</v>
       </c>
       <c r="P45" t="n">
         <v>656</v>
       </c>
       <c r="Q45" t="n">
-        <v>591.8630636593211</v>
+        <v>656</v>
       </c>
       <c r="R45" t="n">
-        <v>591.8630636593211</v>
+        <v>656</v>
       </c>
       <c r="S45" t="n">
-        <v>591.8630636593211</v>
+        <v>656</v>
       </c>
       <c r="T45" t="n">
-        <v>591.8630636593211</v>
+        <v>656</v>
       </c>
       <c r="U45" t="n">
-        <v>591.8630636593211</v>
+        <v>656</v>
       </c>
       <c r="V45" t="n">
-        <v>591.8630636593211</v>
+        <v>656</v>
       </c>
       <c r="W45" t="n">
-        <v>507.3414303838734</v>
+        <v>656</v>
       </c>
       <c r="X45" t="n">
-        <v>507.3414303838734</v>
+        <v>656</v>
       </c>
       <c r="Y45" t="n">
-        <v>341.6848647273051</v>
+        <v>490.3434343432243</v>
       </c>
     </row>
     <row r="46">
@@ -7773,25 +7773,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>47.66986589835295</v>
+        <v>13.12</v>
       </c>
       <c r="C46" t="n">
-        <v>47.66986589835295</v>
+        <v>13.12</v>
       </c>
       <c r="D46" t="n">
-        <v>47.66986589835295</v>
+        <v>13.12</v>
       </c>
       <c r="E46" t="n">
-        <v>47.66986589835295</v>
+        <v>13.12</v>
       </c>
       <c r="F46" t="n">
-        <v>47.66986589835295</v>
+        <v>13.12</v>
       </c>
       <c r="G46" t="n">
-        <v>47.66986589835295</v>
+        <v>13.12</v>
       </c>
       <c r="H46" t="n">
-        <v>47.66986589835295</v>
+        <v>13.12</v>
       </c>
       <c r="I46" t="n">
         <v>13.12</v>
@@ -7830,19 +7830,19 @@
         <v>47.66986589835295</v>
       </c>
       <c r="U46" t="n">
-        <v>47.66986589835295</v>
+        <v>13.12</v>
       </c>
       <c r="V46" t="n">
-        <v>47.66986589835295</v>
+        <v>13.12</v>
       </c>
       <c r="W46" t="n">
-        <v>47.66986589835295</v>
+        <v>13.12</v>
       </c>
       <c r="X46" t="n">
-        <v>47.66986589835295</v>
+        <v>13.12</v>
       </c>
       <c r="Y46" t="n">
-        <v>47.66986589835295</v>
+        <v>13.12</v>
       </c>
     </row>
   </sheetData>
@@ -7967,10 +7967,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>363.9523417085427</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>36.32413159807723</v>
       </c>
       <c r="M2" t="n">
         <v>856.0824090493526</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>346.3574721009829</v>
       </c>
       <c r="Q2" t="n">
-        <v>85.17617797629424</v>
+        <v>66.44691598577684</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,16 +8201,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>157.573739913432</v>
+        <v>63.65657542825833</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>355.0824090493525</v>
+        <v>856.0824090493526</v>
       </c>
       <c r="N5" t="n">
         <v>285.0081138487297</v>
@@ -8219,10 +8219,10 @@
         <v>389.7202916846452</v>
       </c>
       <c r="P5" t="n">
-        <v>346.3574721009829</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>557.4770159857768</v>
+        <v>66.44691598577684</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8447,19 +8447,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>355.0824090493525</v>
+        <v>856.0824090493526</v>
       </c>
       <c r="N8" t="n">
-        <v>442.5818537621617</v>
+        <v>786.0081138487296</v>
       </c>
       <c r="O8" t="n">
-        <v>389.7202916846452</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>346.3574721009829</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>557.4770159857768</v>
+        <v>449.128519684837</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8672,7 +8672,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>120.6470157237802</v>
+        <v>13.19221560746988</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -8684,19 +8684,19 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>442.3568945426216</v>
+        <v>355.0824090493525</v>
       </c>
       <c r="N11" t="n">
-        <v>786.0081138487296</v>
+        <v>285.0081138487297</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>389.7202916846452</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>68.36809390192839</v>
       </c>
       <c r="Q11" t="n">
-        <v>56.47701598577687</v>
+        <v>341.4770159857769</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8757,13 +8757,13 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K12" t="n">
-        <v>161.3831447601762</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L12" t="n">
         <v>388.0893364597981</v>
       </c>
       <c r="M12" t="n">
-        <v>471.6948204301074</v>
+        <v>248.2877158798944</v>
       </c>
       <c r="N12" t="n">
         <v>485.4085271713503</v>
@@ -8915,25 +8915,25 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>363.9523417085427</v>
       </c>
       <c r="L14" t="n">
         <v>330.9802613065326</v>
       </c>
       <c r="M14" t="n">
-        <v>856.0824090493526</v>
+        <v>355.0824090493525</v>
       </c>
       <c r="N14" t="n">
-        <v>786.0081138487296</v>
+        <v>285.0081138487297</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>389.7202916846452</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>56.47701598577687</v>
+        <v>135.1743049809909</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -8991,10 +8991,10 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K15" t="n">
-        <v>204.8885163312921</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L15" t="n">
         <v>388.0893364597981</v>
@@ -9161,16 +9161,16 @@
         <v>856.0824090493526</v>
       </c>
       <c r="N17" t="n">
-        <v>637.3771933053656</v>
+        <v>748.6569016207205</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>389.7202916846452</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>557.4770159857768</v>
+        <v>56.47701598577687</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9234,10 +9234,10 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L18" t="n">
-        <v>379.0288776706983</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M18" t="n">
-        <v>471.6948204301074</v>
+        <v>462.6343616410078</v>
       </c>
       <c r="N18" t="n">
         <v>485.4085271713503</v>
@@ -9386,25 +9386,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>287.3110543644751</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>330.9802613065326</v>
       </c>
       <c r="M20" t="n">
-        <v>778.1467519198316</v>
+        <v>355.0824090493525</v>
       </c>
       <c r="N20" t="n">
-        <v>786.0081138487296</v>
+        <v>285.0081138487297</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>389.7202916846452</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>346.3574721009829</v>
       </c>
       <c r="Q20" t="n">
         <v>56.47701598577687</v>
@@ -9465,10 +9465,10 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J21" t="n">
-        <v>227.4647419277884</v>
+        <v>218.4042831386882</v>
       </c>
       <c r="K21" t="n">
-        <v>286.8197820739152</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L21" t="n">
         <v>388.0893364597981</v>
@@ -9626,10 +9626,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>352.3690794566359</v>
       </c>
       <c r="L23" t="n">
-        <v>330.9802613065326</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>856.0824090493526</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>77.86583413588023</v>
+        <v>56.47701598577687</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9705,10 +9705,10 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K24" t="n">
-        <v>286.8197820739147</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L24" t="n">
-        <v>388.0893364597981</v>
+        <v>379.0288776706986</v>
       </c>
       <c r="M24" t="n">
         <v>471.6948204301074</v>
@@ -9869,7 +9869,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>355.0824090493525</v>
+        <v>269.1974801364421</v>
       </c>
       <c r="N26" t="n">
         <v>141.0081138487297</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>82.48199575204178</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9939,28 +9939,28 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>211.7939847467393</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>11.69189565618446</v>
       </c>
       <c r="L27" t="n">
-        <v>142.9736356534694</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>238.6847782656032</v>
       </c>
       <c r="N27" t="n">
-        <v>117.8940833539598</v>
+        <v>200.8562034777898</v>
       </c>
       <c r="O27" t="n">
-        <v>24.07198444532713</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>159.4074997787493</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>17.27519534353338</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>378.993514918401</v>
+        <v>355.0824090493525</v>
       </c>
       <c r="N29" t="n">
         <v>285.0081138487297</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>56.47701598577687</v>
+        <v>80.38812185482581</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10176,25 +10176,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J30" t="n">
-        <v>211.7939847467165</v>
+        <v>205.1677221204238</v>
       </c>
       <c r="K30" t="n">
-        <v>153.307509014099</v>
+        <v>11.69189565618446</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>152.8343762054507</v>
       </c>
       <c r="M30" t="n">
-        <v>402.6847782656032</v>
+        <v>238.6847782656032</v>
       </c>
       <c r="N30" t="n">
-        <v>200.8562034777898</v>
+        <v>364.8562034777898</v>
       </c>
       <c r="O30" t="n">
-        <v>168.0719844453271</v>
+        <v>4.071984445327132</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>159.4074997787565</v>
       </c>
       <c r="Q30" t="n">
         <v>17.27519534353338</v>
@@ -10331,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>118.5531418265642</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>23.91110586904837</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10346,7 +10346,7 @@
         <v>355.0824090493525</v>
       </c>
       <c r="N32" t="n">
-        <v>311.0130936149945</v>
+        <v>285.0081138487297</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10413,25 +10413,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J33" t="n">
-        <v>47.79398474671648</v>
+        <v>211.7939847467538</v>
       </c>
       <c r="K33" t="n">
-        <v>11.69189565618446</v>
+        <v>153.3075090140616</v>
       </c>
       <c r="L33" t="n">
-        <v>146.2081135791881</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>402.6847782656032</v>
+        <v>238.6847782656032</v>
       </c>
       <c r="N33" t="n">
         <v>364.8562034777898</v>
       </c>
       <c r="O33" t="n">
-        <v>4.071984445327132</v>
+        <v>168.0719844453271</v>
       </c>
       <c r="P33" t="n">
-        <v>159.4074997787264</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>17.27519534353338</v>
@@ -10568,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>120.6470157237802</v>
+        <v>118.5531418265646</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -10580,10 +10580,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>381.0873888156173</v>
+        <v>355.0824090493525</v>
       </c>
       <c r="N35" t="n">
-        <v>285.0081138487297</v>
+        <v>311.0130936149945</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10656,7 +10656,7 @@
         <v>175.6918956561844</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>141.6156133579145</v>
       </c>
       <c r="M36" t="n">
         <v>402.6847782656032</v>
@@ -10665,7 +10665,7 @@
         <v>364.8562034777898</v>
       </c>
       <c r="O36" t="n">
-        <v>141.7566458641284</v>
+        <v>4.071984445327132</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>118.5531418265636</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -10817,7 +10817,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>355.0824090493525</v>
+        <v>371.7299167145825</v>
       </c>
       <c r="N38" t="n">
         <v>285.0081138487297</v>
@@ -10826,10 +10826,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>9.357472101034858</v>
       </c>
       <c r="Q38" t="n">
-        <v>82.48199575204178</v>
+        <v>56.47701598577687</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10887,7 +10887,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>211.7939847467165</v>
+        <v>47.79398474671648</v>
       </c>
       <c r="K39" t="n">
         <v>175.6918956561844</v>
@@ -10896,7 +10896,7 @@
         <v>152.8343762054507</v>
       </c>
       <c r="M39" t="n">
-        <v>238.6847782656032</v>
+        <v>402.6847782656032</v>
       </c>
       <c r="N39" t="n">
         <v>200.8562034777898</v>
@@ -10905,7 +10905,7 @@
         <v>4.071984445327132</v>
       </c>
       <c r="P39" t="n">
-        <v>152.7812371524639</v>
+        <v>148.85028521335</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11042,13 +11042,13 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>120.6470157237802</v>
+        <v>109.1922156074699</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>26.00497976626488</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>82.48199575204178</v>
+        <v>56.47701598577687</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11124,22 +11124,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>47.79398474671648</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>55.69189565618444</v>
+        <v>63.00433155331901</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>229.1431383896502</v>
+        <v>282.6847782656032</v>
       </c>
       <c r="N42" t="n">
-        <v>120.4835126933958</v>
+        <v>80.85620347778976</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>48.07198444532713</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -11291,10 +11291,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>355.0824090493525</v>
+        <v>319.0824090493525</v>
       </c>
       <c r="N44" t="n">
-        <v>285.0081138487297</v>
+        <v>250.1235021112771</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>82.48199575204178</v>
+        <v>56.47701598577687</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11361,25 +11361,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>11.79398474671648</v>
+        <v>211.7939847467902</v>
       </c>
       <c r="K45" t="n">
-        <v>63.6471316556084</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>366.6847782656032</v>
+        <v>384.8928918446437</v>
       </c>
       <c r="N45" t="n">
-        <v>328.8562034777898</v>
+        <v>364.8562034777898</v>
       </c>
       <c r="O45" t="n">
-        <v>168.0719844453271</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>159.4074997788002</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22560,7 +22560,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>65.88174773432711</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -22572,7 +22572,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -22639,10 +22639,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>111.4831557829453</v>
+        <v>39.96455540055615</v>
       </c>
       <c r="S3" t="n">
-        <v>18.04513143267872</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -22679,7 +22679,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>97.33133192677582</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
@@ -22697,7 +22697,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>232.3725770798316</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -22706,7 +22706,7 @@
         <v>44.87548025500894</v>
       </c>
       <c r="N4" t="n">
-        <v>497.2302555995537</v>
+        <v>97.23025559955374</v>
       </c>
       <c r="O4" t="n">
         <v>172.1363181773756</v>
@@ -22715,10 +22715,10 @@
         <v>228.9975366725398</v>
       </c>
       <c r="Q4" t="n">
-        <v>685.371266425598</v>
+        <v>285.371266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>704.8721607680363</v>
+        <v>304.8721607680363</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22727,7 +22727,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>150.9320306187202</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -22736,7 +22736,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -22752,16 +22752,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>404.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>135.7104553179708</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -22797,13 +22797,13 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>56.62882941944662</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>55.21638131302117</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>181.9593204220312</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -22812,10 +22812,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>285.371266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>704.8721607680363</v>
+        <v>304.8721607680363</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>185.0764270975473</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -23055,7 +23055,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -23080,10 +23080,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.1630830448387</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>326.6007664317041</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -23119,7 +23119,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.034255783551544</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -23128,7 +23128,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -23144,7 +23144,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -23180,13 +23180,13 @@
         <v>444.8754802550089</v>
       </c>
       <c r="N10" t="n">
-        <v>497.2302555995537</v>
+        <v>97.23025559955374</v>
       </c>
       <c r="O10" t="n">
-        <v>199.7503890106952</v>
+        <v>172.1363181773756</v>
       </c>
       <c r="P10" t="n">
-        <v>628.9975366725398</v>
+        <v>228.9975366725398</v>
       </c>
       <c r="Q10" t="n">
         <v>285.371266425598</v>
@@ -23198,10 +23198,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>207.9596484734708</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>150.9320306187202</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -23213,7 +23213,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -23241,7 +23241,7 @@
         <v>186.6799853523428</v>
       </c>
       <c r="H11" t="n">
-        <v>180.9758697588038</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>254.2972130284535</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23286,13 +23286,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>421.6286416337032</v>
       </c>
       <c r="X11" t="n">
-        <v>67.31995962430722</v>
+        <v>376.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>295.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23308,7 +23308,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>131.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -23317,10 +23317,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>109.1630830448387</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>110.6007664317041</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -23350,10 +23350,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>295.4831557829453</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>168.2136769184048</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -23362,7 +23362,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>111.9952963271045</v>
       </c>
       <c r="W12" t="n">
         <v>216.3731429098285</v>
@@ -23399,7 +23399,7 @@
         <v>28.56059415300544</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>8.474339216372716</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23420,13 +23420,13 @@
         <v>281.2302555995537</v>
       </c>
       <c r="O13" t="n">
-        <v>356.1363181773756</v>
+        <v>4.538265128847456</v>
       </c>
       <c r="P13" t="n">
         <v>412.9975366725398</v>
       </c>
       <c r="Q13" t="n">
-        <v>136.6203624321523</v>
+        <v>469.371266425598</v>
       </c>
       <c r="R13" t="n">
         <v>488.8721607680363</v>
@@ -23444,7 +23444,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>10.37280983870968</v>
       </c>
       <c r="X13" t="n">
         <v>31.44364543010755</v>
@@ -23469,16 +23469,16 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>37.82759909173977</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>143.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>141.6799853523428</v>
       </c>
       <c r="H14" t="n">
-        <v>135.9758697588038</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,25 +23511,25 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>209.2972130284535</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>320.9593204220312</v>
       </c>
       <c r="U14" t="n">
         <v>388.1351055938368</v>
       </c>
       <c r="V14" t="n">
-        <v>368.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>377.3734759809475</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>197.5085383508541</v>
       </c>
     </row>
     <row r="15">
@@ -23587,7 +23587,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>5.069975611178592</v>
+        <v>5.069975611178563</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -23624,7 +23624,7 @@
         <v>11.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>24.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>19.98090483695654</v>
@@ -23648,28 +23648,28 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>90.69726750204148</v>
+        <v>90.69726750204147</v>
       </c>
       <c r="M16" t="n">
         <v>183.8754802550089</v>
       </c>
       <c r="N16" t="n">
-        <v>236.2302555995537</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>311.1363181773756</v>
+        <v>296.9600140097929</v>
       </c>
       <c r="P16" t="n">
         <v>367.9975366725398</v>
       </c>
       <c r="Q16" t="n">
-        <v>261.8806331400032</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>443.8721607680363</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>92.95125019465871</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23697,10 +23697,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>184.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>99.56268672857004</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>105.6799853523428</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23751,22 +23751,22 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>284.9593204220312</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>352.1351055938368</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>332.8510241668239</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>268.8079834980397</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>214.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -23888,22 +23888,22 @@
         <v>54.69726750204147</v>
       </c>
       <c r="M19" t="n">
-        <v>147.8754802550089</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>200.2302555995537</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>331.9975366725398</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>127.5308682810863</v>
+        <v>407.1736296090814</v>
       </c>
       <c r="S19" t="n">
         <v>56.95125019465871</v>
@@ -23934,25 +23934,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>184.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>152.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>113.3391557398498</v>
       </c>
       <c r="E20" t="n">
-        <v>107.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>107.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>79.3291482679555</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>154.6121835037574</v>
+        <v>173.2972130284535</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -23997,7 +23997,7 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>341.3734759809475</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -24122,7 +24122,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>54.69726750204148</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -24137,13 +24137,13 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>254.2289919426404</v>
+        <v>256.4829746352576</v>
       </c>
       <c r="R22" t="n">
         <v>407.8721607680363</v>
       </c>
       <c r="S22" t="n">
-        <v>56.95125019465871</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24171,22 +24171,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>92.12666307346824</v>
+        <v>184.9993129555745</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>113.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>107.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>107.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>105.6799853523428</v>
+        <v>8.548385358142941</v>
       </c>
       <c r="H23" t="n">
         <v>99.9758697588038</v>
@@ -24231,7 +24231,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>332.8510241668239</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -24359,28 +24359,28 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>54.69726750204147</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>147.8754802550089</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>71.15713852802824</v>
       </c>
       <c r="O25" t="n">
-        <v>275.1363181773756</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>36.04392395992335</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>388.371266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>407.8721607680363</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>56.95125019465871</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24408,19 +24408,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>232.7493047487055</v>
+        <v>337.9993129555745</v>
       </c>
       <c r="C26" t="n">
         <v>305.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>102.3391557398455</v>
+        <v>102.3391557397428</v>
       </c>
       <c r="E26" t="n">
-        <v>260.3632896068686</v>
+        <v>96.363289606769</v>
       </c>
       <c r="F26" t="n">
-        <v>260.8896287080119</v>
+        <v>96.8896287079121</v>
       </c>
       <c r="G26" t="n">
         <v>258.6799853523428</v>
@@ -24456,19 +24456,19 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>39.2011917931186</v>
       </c>
       <c r="S26" t="n">
         <v>326.2972130284535</v>
       </c>
       <c r="T26" t="n">
-        <v>437.9593204220312</v>
+        <v>293.5081204223376</v>
       </c>
       <c r="U26" t="n">
         <v>505.1351055938368</v>
       </c>
       <c r="V26" t="n">
-        <v>321.8510241668201</v>
+        <v>485.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>494.3734759809475</v>
@@ -24477,7 +24477,7 @@
         <v>448.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>203.3174326828021</v>
+        <v>367.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -24487,7 +24487,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>240.5565566463266</v>
+        <v>76.55655664621958</v>
       </c>
       <c r="C27" t="n">
         <v>217.0999124455193</v>
@@ -24496,7 +24496,7 @@
         <v>203.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>198.6720972219126</v>
+        <v>34.67209722180559</v>
       </c>
       <c r="F27" t="n">
         <v>195.6362423378769</v>
@@ -24505,10 +24505,10 @@
         <v>181.1630830448387</v>
       </c>
       <c r="H27" t="n">
-        <v>182.6007664317042</v>
+        <v>18.60076643154787</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>53.27921608002778</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24535,16 +24535,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>203.4831557829352</v>
+        <v>367.4831557829453</v>
       </c>
       <c r="S27" t="n">
-        <v>220.6846575541031</v>
+        <v>311.8566414740453</v>
       </c>
       <c r="T27" t="n">
-        <v>95.0342557835416</v>
+        <v>259.0342557835515</v>
       </c>
       <c r="U27" t="n">
-        <v>92.172435231875</v>
+        <v>111.7212352322553</v>
       </c>
       <c r="V27" t="n">
         <v>270.5106671915202</v>
@@ -24584,10 +24584,10 @@
         <v>100.5605941530054</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>80.47433921637273</v>
       </c>
       <c r="I28" t="n">
-        <v>18.09994742339696</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -24620,16 +24620,16 @@
         <v>209.9512501946587</v>
       </c>
       <c r="T28" t="n">
-        <v>11.31085106919435</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>6.932030618720233</v>
       </c>
       <c r="V28" t="n">
         <v>55.17031021621619</v>
       </c>
       <c r="W28" t="n">
-        <v>82.37280983870968</v>
+        <v>24.37723849620804</v>
       </c>
       <c r="X28" t="n">
         <v>103.4436454301076</v>
@@ -24651,16 +24651,16 @@
         <v>266.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>227.3391557398498</v>
+        <v>63.3391557397091</v>
       </c>
       <c r="E29" t="n">
         <v>221.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>57.8896287080056</v>
+        <v>221.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>75.42997714549193</v>
+        <v>55.67998535213349</v>
       </c>
       <c r="H29" t="n">
         <v>213.9758697588038</v>
@@ -24702,19 +24702,19 @@
         <v>398.9593204220312</v>
       </c>
       <c r="U29" t="n">
-        <v>302.1351055938223</v>
+        <v>466.1351055938368</v>
       </c>
       <c r="V29" t="n">
-        <v>282.8510241668141</v>
+        <v>446.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>455.3734759809475</v>
+        <v>291.373475980807</v>
       </c>
       <c r="X29" t="n">
         <v>409.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>328.3174326828064</v>
+        <v>184.0674244764156</v>
       </c>
     </row>
     <row r="30">
@@ -24724,10 +24724,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>37.55655664631581</v>
+        <v>37.55655664618587</v>
       </c>
       <c r="C30" t="n">
-        <v>178.0999124455193</v>
+        <v>14.09991244537866</v>
       </c>
       <c r="D30" t="n">
         <v>164.9376868977026</v>
@@ -24736,16 +24736,16 @@
         <v>159.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>12.18504233836876</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>142.1630830448387</v>
       </c>
       <c r="H30" t="n">
         <v>143.6007664317042</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>14.27921608002778</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24778,7 +24778,7 @@
         <v>272.8566414740453</v>
       </c>
       <c r="T30" t="n">
-        <v>220.0342557835515</v>
+        <v>56.03425578334111</v>
       </c>
       <c r="U30" t="n">
         <v>217.1724352318849</v>
@@ -24790,7 +24790,7 @@
         <v>249.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>77.49008090814172</v>
+        <v>236.8627394453875</v>
       </c>
       <c r="Y30" t="n">
         <v>216.3913927661343</v>
@@ -24833,7 +24833,7 @@
         <v>49.37257707983158</v>
       </c>
       <c r="L31" t="n">
-        <v>168.6972675020415</v>
+        <v>161.5212483977078</v>
       </c>
       <c r="M31" t="n">
         <v>261.8754802550089</v>
@@ -24854,19 +24854,19 @@
         <v>521.8721607680363</v>
       </c>
       <c r="S31" t="n">
-        <v>84.27799961850721</v>
+        <v>6.951250194444242</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>24.95964847347083</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>16.17031021621619</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>43.37280983870968</v>
       </c>
       <c r="X31" t="n">
         <v>64.44364543010755</v>
@@ -24882,16 +24882,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>134.999312955563</v>
+        <v>134.9993129555372</v>
       </c>
       <c r="C32" t="n">
-        <v>122.2245700361482</v>
+        <v>266.4745782429939</v>
       </c>
       <c r="D32" t="n">
         <v>227.3391557398498</v>
       </c>
       <c r="E32" t="n">
-        <v>57.36328960685887</v>
+        <v>57.3632896068313</v>
       </c>
       <c r="F32" t="n">
         <v>221.8896287080119</v>
@@ -24900,7 +24900,7 @@
         <v>219.6799853523428</v>
       </c>
       <c r="H32" t="n">
-        <v>49.97586975878949</v>
+        <v>213.9758697588038</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -24939,7 +24939,7 @@
         <v>398.9593204220312</v>
       </c>
       <c r="U32" t="n">
-        <v>466.1351055938368</v>
+        <v>321.8850973870675</v>
       </c>
       <c r="V32" t="n">
         <v>446.8510241668239</v>
@@ -24948,7 +24948,7 @@
         <v>455.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>409.2818334606677</v>
+        <v>245.2818334606303</v>
       </c>
       <c r="Y32" t="n">
         <v>328.3174326828064</v>
@@ -24964,10 +24964,10 @@
         <v>201.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>14.09991244550724</v>
+        <v>178.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>164.9376868977026</v>
+        <v>0.9376868975401749</v>
       </c>
       <c r="E33" t="n">
         <v>159.6720972219126</v>
@@ -24979,10 +24979,10 @@
         <v>142.1630830448387</v>
       </c>
       <c r="H33" t="n">
-        <v>13.42878251177623</v>
+        <v>143.6007664317041</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>14.27921608002778</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25009,25 +25009,25 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>164.4831557829299</v>
+        <v>328.4831557829453</v>
       </c>
       <c r="S33" t="n">
         <v>272.8566414740453</v>
       </c>
       <c r="T33" t="n">
-        <v>56.03425578353472</v>
+        <v>75.58305578403869</v>
       </c>
       <c r="U33" t="n">
         <v>217.1724352318848</v>
       </c>
       <c r="V33" t="n">
-        <v>231.5106671915202</v>
+        <v>67.51066719135781</v>
       </c>
       <c r="W33" t="n">
         <v>249.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>236.8627394453875</v>
+        <v>72.8627394452252</v>
       </c>
       <c r="Y33" t="n">
         <v>216.3913927661343</v>
@@ -25040,7 +25040,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>104.1138003370787</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>89.72524664804467</v>
@@ -25052,13 +25052,13 @@
         <v>97.98090483695654</v>
       </c>
       <c r="F34" t="n">
-        <v>66.2701995445959</v>
+        <v>91.38285596774193</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>61.56059415300544</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>41.47433921637273</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -25079,7 +25079,7 @@
         <v>314.2302555995537</v>
       </c>
       <c r="O34" t="n">
-        <v>389.1363181773756</v>
+        <v>296.7700704097496</v>
       </c>
       <c r="P34" t="n">
         <v>445.9975366725398</v>
@@ -25094,7 +25094,7 @@
         <v>170.9512501946587</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>24.95964847347082</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -25103,7 +25103,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>43.37280983870968</v>
       </c>
       <c r="X34" t="n">
         <v>64.44364543010755</v>
@@ -25122,22 +25122,22 @@
         <v>298.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>102.4745782429814</v>
+        <v>266.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>227.3391557398498</v>
+        <v>63.33915573980514</v>
       </c>
       <c r="E35" t="n">
         <v>221.3632896068686</v>
       </c>
       <c r="F35" t="n">
-        <v>221.8896287080119</v>
+        <v>77.63962050126446</v>
       </c>
       <c r="G35" t="n">
-        <v>55.67998535232664</v>
+        <v>219.6799853523428</v>
       </c>
       <c r="H35" t="n">
-        <v>69.72586155196277</v>
+        <v>213.9758697588038</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25170,13 +25170,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>287.2972130284535</v>
+        <v>123.2972130284089</v>
       </c>
       <c r="T35" t="n">
         <v>398.9593204220312</v>
       </c>
       <c r="U35" t="n">
-        <v>466.1351055938368</v>
+        <v>302.1351055937921</v>
       </c>
       <c r="V35" t="n">
         <v>446.8510241668239</v>
@@ -25188,7 +25188,7 @@
         <v>409.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>164.3174326827948</v>
+        <v>328.3174326828064</v>
       </c>
     </row>
     <row r="36">
@@ -25201,25 +25201,25 @@
         <v>201.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>178.0999124455193</v>
+        <v>14.09991244530954</v>
       </c>
       <c r="D36" t="n">
         <v>164.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>159.6720972219126</v>
+        <v>15.22089722268612</v>
       </c>
       <c r="F36" t="n">
         <v>156.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>142.1630830448387</v>
       </c>
       <c r="H36" t="n">
         <v>143.6007664317042</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>14.27921608002778</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25246,7 +25246,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>176.4742549078357</v>
+        <v>328.4831557829453</v>
       </c>
       <c r="S36" t="n">
         <v>272.8566414740453</v>
@@ -25255,16 +25255,16 @@
         <v>220.0342557835515</v>
       </c>
       <c r="U36" t="n">
-        <v>217.1724352318849</v>
+        <v>53.17243523153081</v>
       </c>
       <c r="V36" t="n">
-        <v>67.51066719150731</v>
+        <v>67.51066719131052</v>
       </c>
       <c r="W36" t="n">
         <v>249.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>72.86273944537652</v>
+        <v>236.8627394453875</v>
       </c>
       <c r="Y36" t="n">
         <v>216.3913927661343</v>
@@ -25277,7 +25277,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>104.1138003370787</v>
+        <v>55.46344201615774</v>
       </c>
       <c r="C37" t="n">
         <v>89.72524664804467</v>
@@ -25286,16 +25286,16 @@
         <v>102.5362180555555</v>
       </c>
       <c r="E37" t="n">
-        <v>59.31770038983726</v>
+        <v>97.98090483695654</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>91.38285596774193</v>
       </c>
       <c r="G37" t="n">
         <v>61.56059415300544</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>41.47433921637271</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -25316,7 +25316,7 @@
         <v>314.2302555995537</v>
       </c>
       <c r="O37" t="n">
-        <v>389.1363181773756</v>
+        <v>225.1363181773756</v>
       </c>
       <c r="P37" t="n">
         <v>445.9975366725398</v>
@@ -25331,13 +25331,13 @@
         <v>170.9512501946587</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>24.95964847347083</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>16.17031021621619</v>
       </c>
       <c r="W37" t="n">
         <v>43.37280983870968</v>
@@ -25362,13 +25362,13 @@
         <v>266.4745782429939</v>
       </c>
       <c r="D38" t="n">
-        <v>227.3391557398498</v>
+        <v>63.33915573959632</v>
       </c>
       <c r="E38" t="n">
         <v>221.3632896068686</v>
       </c>
       <c r="F38" t="n">
-        <v>221.8896287080119</v>
+        <v>57.88962870777289</v>
       </c>
       <c r="G38" t="n">
         <v>219.6799853523428</v>
@@ -25413,16 +25413,16 @@
         <v>398.9593204220312</v>
       </c>
       <c r="U38" t="n">
-        <v>302.1351055938187</v>
+        <v>321.8850973877012</v>
       </c>
       <c r="V38" t="n">
-        <v>282.8510241668096</v>
+        <v>446.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>291.3734759809342</v>
+        <v>291.3734759806943</v>
       </c>
       <c r="X38" t="n">
-        <v>265.031825253832</v>
+        <v>409.2818334606677</v>
       </c>
       <c r="Y38" t="n">
         <v>328.3174326828064</v>
@@ -25441,22 +25441,22 @@
         <v>178.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>164.9376868977026</v>
+        <v>13.12272923608609</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>159.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>156.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>142.1630830448387</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>143.6007664317041</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>14.27921608002778</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25495,13 +25495,13 @@
         <v>217.1724352318848</v>
       </c>
       <c r="V39" t="n">
-        <v>67.51066719150595</v>
+        <v>67.51066719126686</v>
       </c>
       <c r="W39" t="n">
-        <v>236.637105688326</v>
+        <v>249.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>236.8627394453875</v>
+        <v>72.86273944513425</v>
       </c>
       <c r="Y39" t="n">
         <v>216.3913927661343</v>
@@ -25550,7 +25550,7 @@
         <v>261.8754802550089</v>
       </c>
       <c r="N40" t="n">
-        <v>314.2302555995537</v>
+        <v>150.2302555991184</v>
       </c>
       <c r="O40" t="n">
         <v>389.1363181773756</v>
@@ -25559,25 +25559,25 @@
         <v>445.9975366725398</v>
       </c>
       <c r="Q40" t="n">
-        <v>415.6980158494466</v>
+        <v>502.371266425598</v>
       </c>
       <c r="R40" t="n">
         <v>521.8721607680363</v>
       </c>
       <c r="S40" t="n">
-        <v>170.9512501946587</v>
+        <v>163.7752310905458</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>24.95964847347082</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>16.17031021621619</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>43.37280983870968</v>
       </c>
       <c r="X40" t="n">
         <v>64.44364543010755</v>
@@ -25593,25 +25593,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>280.7493047487154</v>
+        <v>361.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>329.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>290.3391557398498</v>
+        <v>126.3391557395752</v>
       </c>
       <c r="E41" t="n">
         <v>284.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>120.8896287080062</v>
+        <v>284.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>282.6799853523428</v>
+        <v>118.6799853518968</v>
       </c>
       <c r="H41" t="n">
-        <v>276.9758697588038</v>
+        <v>132.5246697597989</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,13 +25641,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>63.2011917931186</v>
       </c>
       <c r="S41" t="n">
         <v>350.2972130284535</v>
       </c>
       <c r="T41" t="n">
-        <v>297.9593204220201</v>
+        <v>461.9593204220312</v>
       </c>
       <c r="U41" t="n">
         <v>529.1351055938368</v>
@@ -25656,10 +25656,10 @@
         <v>509.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>518.3734759809475</v>
+        <v>354.3734759806731</v>
       </c>
       <c r="X41" t="n">
-        <v>308.2818334606621</v>
+        <v>472.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>391.3174326828064</v>
@@ -25678,10 +25678,10 @@
         <v>241.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>160.7657029777525</v>
+        <v>227.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>222.6720972219126</v>
+        <v>58.67209722165251</v>
       </c>
       <c r="F42" t="n">
         <v>219.6362423378769</v>
@@ -25690,10 +25690,10 @@
         <v>205.1630830448387</v>
       </c>
       <c r="H42" t="n">
-        <v>206.6007664317042</v>
+        <v>42.60076643124933</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>77.27921608002778</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25723,22 +25723,22 @@
         <v>391.4831557829453</v>
       </c>
       <c r="S42" t="n">
-        <v>171.856641474035</v>
+        <v>335.8566414740453</v>
       </c>
       <c r="T42" t="n">
-        <v>283.0342557835515</v>
+        <v>119.0342557831028</v>
       </c>
       <c r="U42" t="n">
         <v>280.1724352318848</v>
       </c>
       <c r="V42" t="n">
-        <v>130.5106671915138</v>
+        <v>294.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>312.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>135.8627394453821</v>
+        <v>155.4115394465512</v>
       </c>
       <c r="Y42" t="n">
         <v>279.3913927661343</v>
@@ -25766,7 +25766,7 @@
         <v>154.3828559677419</v>
       </c>
       <c r="G43" t="n">
-        <v>38.95985753235627</v>
+        <v>124.5605941530054</v>
       </c>
       <c r="H43" t="n">
         <v>104.4743392163727</v>
@@ -25796,7 +25796,7 @@
         <v>508.9975366725398</v>
       </c>
       <c r="Q43" t="n">
-        <v>565.371266425598</v>
+        <v>448.8384991862286</v>
       </c>
       <c r="R43" t="n">
         <v>584.8721607680363</v>
@@ -25808,7 +25808,7 @@
         <v>87.95964847347084</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>30.93203061872023</v>
       </c>
       <c r="V43" t="n">
         <v>79.17031021621619</v>
@@ -25833,7 +25833,7 @@
         <v>445.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>413.4745782429939</v>
+        <v>249.4745782427931</v>
       </c>
       <c r="D44" t="n">
         <v>374.3391557398498</v>
@@ -25842,13 +25842,13 @@
         <v>368.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>204.8896287080072</v>
+        <v>204.889628707811</v>
       </c>
       <c r="G44" t="n">
-        <v>202.6799853523371</v>
+        <v>202.6799853520916</v>
       </c>
       <c r="H44" t="n">
-        <v>199.7258615519328</v>
+        <v>216.5246697594568</v>
       </c>
       <c r="I44" t="n">
         <v>72.54519988368963</v>
@@ -25878,7 +25878,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>147.2011917931186</v>
       </c>
       <c r="S44" t="n">
         <v>434.2972130284535</v>
@@ -25909,10 +25909,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>348.5565566463266</v>
+        <v>184.5565566461185</v>
       </c>
       <c r="C45" t="n">
-        <v>325.0999124455193</v>
+        <v>180.6487124462207</v>
       </c>
       <c r="D45" t="n">
         <v>311.9376868977026</v>
@@ -25924,13 +25924,13 @@
         <v>303.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>289.1630830448387</v>
+        <v>125.1630830445534</v>
       </c>
       <c r="H45" t="n">
-        <v>126.6007664316999</v>
+        <v>290.6007664317041</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>161.2792160800278</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25954,7 +25954,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>63.49556697727203</v>
       </c>
       <c r="R45" t="n">
         <v>475.4831557829453</v>
@@ -25972,13 +25972,13 @@
         <v>378.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>312.6967259671353</v>
+        <v>396.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>383.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>199.3913927661318</v>
+        <v>199.3913927659264</v>
       </c>
     </row>
     <row r="46">
@@ -26009,7 +26009,7 @@
         <v>188.4743392163727</v>
       </c>
       <c r="I46" t="n">
-        <v>91.89558018402755</v>
+        <v>126.099947423397</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -26045,7 +26045,7 @@
         <v>171.9596484734708</v>
       </c>
       <c r="U46" t="n">
-        <v>114.9320306187202</v>
+        <v>80.72766337935082</v>
       </c>
       <c r="V46" t="n">
         <v>163.1703102162162</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>893887.7122675846</v>
+        <v>893887.7122675849</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1540179.469909463</v>
+        <v>1540179.469909464</v>
       </c>
     </row>
     <row r="4">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2682420.603450857</v>
+        <v>2682420.603450858</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3325267.576800838</v>
+        <v>3325267.576800839</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3987622.893429538</v>
+        <v>3987622.89342954</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4630438.655576967</v>
+        <v>4630438.655576966</v>
       </c>
     </row>
     <row r="9">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5482260.810596924</v>
+        <v>5482260.810596926</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5934020.634632667</v>
+        <v>5934020.634632669</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6355361.889870532</v>
+        <v>6355361.889870533</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6776703.145108399</v>
+        <v>6776703.145108397</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7198044.400346264</v>
+        <v>7198044.400346262</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7511170.207121936</v>
+        <v>7511170.207121934</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7747254.779734101</v>
+        <v>7747254.779734098</v>
       </c>
     </row>
   </sheetData>
@@ -26281,37 +26281,37 @@
         <v>1204061.685640727</v>
       </c>
       <c r="F2" t="n">
-        <v>1329483.956399961</v>
+        <v>1329483.95639996</v>
       </c>
       <c r="G2" t="n">
-        <v>1402507.117412574</v>
+        <v>1402507.117412575</v>
       </c>
       <c r="H2" t="n">
         <v>1402507.117412575</v>
       </c>
       <c r="I2" t="n">
-        <v>1402507.117412574</v>
+        <v>1402507.117412575</v>
       </c>
       <c r="J2" t="n">
-        <v>805262.8289573188</v>
+        <v>805262.8289573184</v>
       </c>
       <c r="K2" t="n">
-        <v>919290.0114280803</v>
+        <v>919290.0114280801</v>
       </c>
       <c r="L2" t="n">
         <v>919290.0114280806</v>
       </c>
       <c r="M2" t="n">
-        <v>919290.0114280803</v>
+        <v>919290.0114280804</v>
       </c>
       <c r="N2" t="n">
-        <v>919290.0114280806</v>
+        <v>919290.0114280807</v>
       </c>
       <c r="O2" t="n">
-        <v>734762.6638373183</v>
+        <v>734762.6638373187</v>
       </c>
       <c r="P2" t="n">
-        <v>477851.913976624</v>
+        <v>477851.9139766244</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>653717.4975417332</v>
+        <v>657889.0683999022</v>
       </c>
       <c r="C4" t="n">
-        <v>652086.3533539857</v>
+        <v>656257.9242121548</v>
       </c>
       <c r="D4" t="n">
-        <v>650452.9964173387</v>
+        <v>654624.567275508</v>
       </c>
       <c r="E4" t="n">
-        <v>533603.9138788399</v>
+        <v>536833.458726464</v>
       </c>
       <c r="F4" t="n">
-        <v>600969.6490493818</v>
+        <v>604763.614634054</v>
       </c>
       <c r="G4" t="n">
-        <v>639456.7222021588</v>
+        <v>643579.8960575351</v>
       </c>
       <c r="H4" t="n">
-        <v>637826.8175333203</v>
+        <v>641949.9913886967</v>
       </c>
       <c r="I4" t="n">
-        <v>636194.6374911093</v>
+        <v>640317.8113464857</v>
       </c>
       <c r="J4" t="n">
-        <v>308160.7644396867</v>
+        <v>309586.9904567241</v>
       </c>
       <c r="K4" t="n">
-        <v>368989.8175065434</v>
+        <v>370928.5446883768</v>
       </c>
       <c r="L4" t="n">
-        <v>367918.0098981324</v>
+        <v>369856.7370799659</v>
       </c>
       <c r="M4" t="n">
-        <v>366844.6703861997</v>
+        <v>368783.3975680331</v>
       </c>
       <c r="N4" t="n">
-        <v>365769.7875905294</v>
+        <v>367708.5147723629</v>
       </c>
       <c r="O4" t="n">
-        <v>273707.8683262959</v>
+        <v>275248.294724535</v>
       </c>
       <c r="P4" t="n">
-        <v>162641.1958225947</v>
+        <v>164469.2077367871</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>248790.8100405489</v>
+        <v>244619.2391823801</v>
       </c>
       <c r="C6" t="n">
-        <v>688073.9542282963</v>
+        <v>683902.3833701274</v>
       </c>
       <c r="D6" t="n">
-        <v>689707.3111649433</v>
+        <v>685535.7403067736</v>
       </c>
       <c r="E6" t="n">
-        <v>443195.6677618872</v>
+        <v>439966.1229142635</v>
       </c>
       <c r="F6" t="n">
-        <v>634269.0983505793</v>
+        <v>630475.1327659062</v>
       </c>
       <c r="G6" t="n">
-        <v>672978.7022104156</v>
+        <v>668855.5283550398</v>
       </c>
       <c r="H6" t="n">
-        <v>703408.606879255</v>
+        <v>699285.4330238784</v>
       </c>
       <c r="I6" t="n">
-        <v>705040.7869214651</v>
+        <v>700917.6130660889</v>
       </c>
       <c r="J6" t="n">
-        <v>361054.5285176321</v>
+        <v>359628.3025005943</v>
       </c>
       <c r="K6" t="n">
-        <v>451901.9669215369</v>
+        <v>449963.2397397033</v>
       </c>
       <c r="L6" t="n">
-        <v>491373.7745299482</v>
+        <v>489435.0473481147</v>
       </c>
       <c r="M6" t="n">
-        <v>521247.1140418806</v>
+        <v>519308.3868600473</v>
       </c>
       <c r="N6" t="n">
-        <v>522321.9968375512</v>
+        <v>520383.2696557178</v>
       </c>
       <c r="O6" t="n">
-        <v>435152.9155110224</v>
+        <v>433612.4891127837</v>
       </c>
       <c r="P6" t="n">
-        <v>296370.6341540294</v>
+        <v>294542.6222398374</v>
       </c>
     </row>
   </sheetData>
@@ -26978,7 +26978,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
         <v>216</v>
@@ -27442,13 +27442,13 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F2" t="n">
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>400</v>
+        <v>42.51209909157842</v>
       </c>
       <c r="H2" t="n">
         <v>396.9758697588038</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>183.2011917931186</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27502,7 +27502,7 @@
         <v>400</v>
       </c>
       <c r="Y2" t="n">
-        <v>400</v>
+        <v>10.31743268280638</v>
       </c>
     </row>
     <row r="3">
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27524,7 +27524,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.1630830448387</v>
@@ -27533,7 +27533,7 @@
         <v>326.6007664317041</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>197.2792160800278</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,7 +27560,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>337.2048300434899</v>
       </c>
     </row>
     <row r="4">
@@ -27600,7 +27600,7 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>183.6495729101807</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -27618,7 +27618,7 @@
         <v>1.10114555721924</v>
       </c>
       <c r="K4" t="n">
-        <v>232.3725770798316</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>351.6972675020415</v>
@@ -27627,7 +27627,7 @@
         <v>400</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O4" t="n">
         <v>400</v>
@@ -27636,10 +27636,10 @@
         <v>400</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S4" t="n">
         <v>353.9512501946587</v>
@@ -27648,7 +27648,7 @@
         <v>207.9596484734708</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9320306187202</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27657,7 +27657,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27676,13 +27676,13 @@
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>269.1791733900411</v>
+        <v>365.374966521547</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>183.2011917931186</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27749,7 +27749,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
@@ -27758,19 +27758,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.1630830448387</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>197.2792160800278</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,19 +27797,19 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>384.9365988100682</v>
+        <v>10.48315578294532</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>293.8956033266703</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27876,7 +27876,7 @@
         <v>400</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S7" t="n">
         <v>353.9512501946587</v>
@@ -27916,19 +27916,19 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>396.9758697588038</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>108.5451998836896</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>183.2011917931186</v>
+        <v>169.4878879539738</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27964,7 +27964,7 @@
         <v>400</v>
       </c>
       <c r="U8" t="n">
-        <v>388.2016255837019</v>
+        <v>400</v>
       </c>
       <c r="V8" t="n">
         <v>400</v>
@@ -27986,25 +27986,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>278.344928985441</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.1630830448387</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>326.6007664317041</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -28031,19 +28031,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>99.49556697727203</v>
       </c>
       <c r="R9" t="n">
         <v>10.48315578294532</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>180.0174963286673</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>272.7252466480447</v>
@@ -28101,13 +28101,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O10" t="n">
-        <v>372.3859291666804</v>
+        <v>400</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q10" t="n">
         <v>400</v>
@@ -28119,10 +28119,10 @@
         <v>353.9512501946587</v>
       </c>
       <c r="T10" t="n">
-        <v>207.9596484734708</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9320306187202</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
@@ -28134,7 +28134,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -28168,28 +28168,28 @@
         <v>216</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>146.4818856631807</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>216</v>
       </c>
-      <c r="K11" t="n">
-        <v>193.8409856401748</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="Q11" t="n">
         <v>216</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>216</v>
@@ -28244,7 +28244,7 @@
         <v>216</v>
       </c>
       <c r="I12" t="n">
-        <v>216</v>
+        <v>197.2792160800278</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28253,7 +28253,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>101.7450397456525</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28262,13 +28262,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>122.3901856444234</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>216</v>
+        <v>99.49556697727203</v>
       </c>
       <c r="R12" t="n">
         <v>216</v>
@@ -28405,7 +28405,7 @@
         <v>229.1922156074699</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>113.2200875548199</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>204.590009943222</v>
+        <v>261</v>
       </c>
       <c r="S14" t="n">
         <v>261</v>
@@ -28484,16 +28484,16 @@
         <v>197.2792160800278</v>
       </c>
       <c r="J15" t="n">
-        <v>47.79398474671648</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.7281208398629815</v>
       </c>
       <c r="M15" t="n">
-        <v>109.8861695299284</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>261</v>
+        <v>99.49556697727203</v>
       </c>
       <c r="R15" t="n">
         <v>261</v>
@@ -28697,19 +28697,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>297</v>
       </c>
       <c r="D18" t="n">
-        <v>68.66376250552487</v>
+        <v>297</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="F18" t="n">
-        <v>297</v>
+        <v>68.66376250552531</v>
       </c>
       <c r="G18" t="n">
         <v>297</v>
@@ -28934,13 +28934,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>68.66376250552337</v>
+        <v>297</v>
       </c>
       <c r="C21" t="n">
         <v>297</v>
       </c>
       <c r="D21" t="n">
-        <v>297</v>
+        <v>168.1593294827968</v>
       </c>
       <c r="E21" t="n">
         <v>297</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>99.49556697727203</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>297</v>
@@ -28991,10 +28991,10 @@
         <v>297</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
         <v>297</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>297</v>
@@ -29171,10 +29171,10 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
         <v>297</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>297</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>99.49556697727203</v>
       </c>
       <c r="R24" t="n">
         <v>297</v>
@@ -29228,10 +29228,10 @@
         <v>297</v>
       </c>
       <c r="U24" t="n">
-        <v>168.1593294827963</v>
+        <v>297</v>
       </c>
       <c r="V24" t="n">
-        <v>297</v>
+        <v>68.6637625055248</v>
       </c>
       <c r="W24" t="n">
         <v>297</v>
@@ -29350,7 +29350,7 @@
         <v>144</v>
       </c>
       <c r="I26" t="n">
-        <v>108.5451998836896</v>
+        <v>134.5501796499545</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29362,7 +29362,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>85.88492891291034</v>
       </c>
       <c r="N26" t="n">
         <v>144</v>
@@ -29374,7 +29374,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>56.47701598577687</v>
       </c>
       <c r="R26" t="n">
         <v>144</v>
@@ -29432,22 +29432,22 @@
         <v>144</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>144</v>
       </c>
-      <c r="K27" t="n">
-        <v>144</v>
-      </c>
-      <c r="L27" t="n">
-        <v>9.860740551981365</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>144</v>
+        <v>125.7756650017417</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -29587,7 +29587,7 @@
         <v>183</v>
       </c>
       <c r="I29" t="n">
-        <v>110.6390737809059</v>
+        <v>110.6390737809056</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29824,7 +29824,7 @@
         <v>183</v>
       </c>
       <c r="I32" t="n">
-        <v>110.6390737809057</v>
+        <v>110.6390737809061</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -30061,7 +30061,7 @@
         <v>183</v>
       </c>
       <c r="I35" t="n">
-        <v>108.5451998836896</v>
+        <v>110.6390737809052</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>103.4265189163854</v>
+        <v>99.49556697727203</v>
       </c>
       <c r="R36" t="n">
         <v>183</v>
@@ -30298,7 +30298,7 @@
         <v>183</v>
       </c>
       <c r="I38" t="n">
-        <v>110.6390737809063</v>
+        <v>108.5451998836896</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>99.49556697727203</v>
+        <v>103.4265189163859</v>
       </c>
       <c r="R39" t="n">
         <v>183</v>
@@ -30535,7 +30535,7 @@
         <v>120</v>
       </c>
       <c r="I41" t="n">
-        <v>108.5451998836896</v>
+        <v>120</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30617,10 +30617,10 @@
         <v>120</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>47.79398474671648</v>
       </c>
       <c r="K42" t="n">
-        <v>120</v>
+        <v>14.30317746078001</v>
       </c>
       <c r="L42" t="n">
         <v>120</v>
@@ -30629,7 +30629,7 @@
         <v>120</v>
       </c>
       <c r="N42" t="n">
-        <v>80.372690784394</v>
+        <v>120</v>
       </c>
       <c r="O42" t="n">
         <v>120</v>
@@ -30638,7 +30638,7 @@
         <v>120</v>
       </c>
       <c r="Q42" t="n">
-        <v>120</v>
+        <v>116.7707623208054</v>
       </c>
       <c r="R42" t="n">
         <v>120</v>
@@ -30778,16 +30778,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>26.00497976626488</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>34.88461173745257</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -30854,25 +30854,25 @@
         <v>36</v>
       </c>
       <c r="J45" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>17.66037735849057</v>
+        <v>11.69189565618446</v>
       </c>
       <c r="L45" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4.071984445327132</v>
       </c>
       <c r="P45" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>36</v>
@@ -35451,31 +35451,31 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>107.4548001163104</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>272.3988631016433</v>
+        <v>56.39886310164335</v>
       </c>
       <c r="K11" t="n">
-        <v>330.8886439316321</v>
+        <v>137.0476582914573</v>
       </c>
       <c r="L11" t="n">
-        <v>386.0197386934675</v>
+        <v>316.5016243566481</v>
       </c>
       <c r="M11" t="n">
-        <v>87.27448549326917</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>501</v>
       </c>
-      <c r="O11" t="n">
-        <v>111.2797083153548</v>
-      </c>
       <c r="P11" t="n">
-        <v>154.6425278990171</v>
+        <v>439.0106218009454</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>501</v>
       </c>
       <c r="R11" t="n">
         <v>32.7988082068814</v>
@@ -35530,31 +35530,31 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>18.72078391997222</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>179.670757181072</v>
       </c>
       <c r="K12" t="n">
-        <v>149.6912491039918</v>
+        <v>284.1883452068291</v>
       </c>
       <c r="L12" t="n">
-        <v>399.2549602543474</v>
+        <v>501</v>
       </c>
       <c r="M12" t="n">
-        <v>233.0100421645043</v>
+        <v>9.602937614291211</v>
       </c>
       <c r="N12" t="n">
         <v>284.5523236935605</v>
       </c>
       <c r="O12" t="n">
-        <v>378.6098143555766</v>
+        <v>501</v>
       </c>
       <c r="P12" t="n">
         <v>223.743212061823</v>
       </c>
       <c r="Q12" t="n">
-        <v>116.504433022728</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35691,31 +35691,31 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>56.39886310164335</v>
+        <v>169.6189506564633</v>
       </c>
       <c r="K14" t="n">
-        <v>137.0476582914573</v>
+        <v>501</v>
       </c>
       <c r="L14" t="n">
         <v>501</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>501</v>
-      </c>
-      <c r="N14" t="n">
-        <v>501</v>
-      </c>
-      <c r="O14" t="n">
-        <v>111.2797083153548</v>
       </c>
       <c r="P14" t="n">
         <v>154.6425278990171</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>78.69728899521407</v>
       </c>
       <c r="R14" t="n">
-        <v>21.38881815010336</v>
+        <v>77.79880820688143</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -35770,16 +35770,16 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>179.670757181072</v>
       </c>
       <c r="K15" t="n">
-        <v>193.1966206751076</v>
+        <v>284.1883452068291</v>
       </c>
       <c r="L15" t="n">
-        <v>399.2549602543474</v>
+        <v>399.9830810942104</v>
       </c>
       <c r="M15" t="n">
-        <v>342.8962116944327</v>
+        <v>233.0100421645043</v>
       </c>
       <c r="N15" t="n">
         <v>284.5523236935605</v>
@@ -35791,7 +35791,7 @@
         <v>223.743212061823</v>
       </c>
       <c r="Q15" t="n">
-        <v>161.504433022728</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35843,16 +35843,16 @@
         <v>16.43940584699456</v>
       </c>
       <c r="H16" t="n">
-        <v>36.52566078362727</v>
+        <v>36.52566078362729</v>
       </c>
       <c r="I16" t="n">
-        <v>98.90005257660303</v>
+        <v>98.90005257660304</v>
       </c>
       <c r="J16" t="n">
         <v>259.8988544427808</v>
       </c>
       <c r="K16" t="n">
-        <v>28.62742292016841</v>
+        <v>28.62742292016842</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>53.04035152652918</v>
+        <v>53.04035152652917</v>
       </c>
       <c r="U16" t="n">
         <v>110.0679693812798</v>
@@ -35940,16 +35940,16 @@
         <v>501</v>
       </c>
       <c r="N17" t="n">
-        <v>352.3690794566359</v>
+        <v>463.6487877719908</v>
       </c>
       <c r="O17" t="n">
-        <v>111.2797083153548</v>
+        <v>501</v>
       </c>
       <c r="P17" t="n">
         <v>154.6425278990171</v>
       </c>
       <c r="Q17" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36013,10 +36013,10 @@
         <v>284.1883452068291</v>
       </c>
       <c r="L18" t="n">
-        <v>390.1945014652475</v>
+        <v>399.2549602543474</v>
       </c>
       <c r="M18" t="n">
-        <v>233.0100421645043</v>
+        <v>223.9495833754046</v>
       </c>
       <c r="N18" t="n">
         <v>284.5523236935605</v>
@@ -36165,25 +36165,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>486.7035996878001</v>
+        <v>56.39886310164335</v>
       </c>
       <c r="K20" t="n">
-        <v>137.0476582914573</v>
+        <v>424.3587126559324</v>
       </c>
       <c r="L20" t="n">
-        <v>170.0197386934674</v>
+        <v>501</v>
       </c>
       <c r="M20" t="n">
-        <v>423.0643428704792</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>501</v>
       </c>
-      <c r="O20" t="n">
-        <v>111.2797083153548</v>
-      </c>
       <c r="P20" t="n">
-        <v>154.6425278990171</v>
+        <v>501</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36244,10 +36244,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>179.670757181072</v>
+        <v>170.6102983919717</v>
       </c>
       <c r="K21" t="n">
-        <v>275.1278864177307</v>
+        <v>284.1883452068291</v>
       </c>
       <c r="L21" t="n">
         <v>399.2549602543474</v>
@@ -36405,10 +36405,10 @@
         <v>56.39886310164335</v>
       </c>
       <c r="K23" t="n">
-        <v>137.0476582914573</v>
+        <v>489.4167377480932</v>
       </c>
       <c r="L23" t="n">
-        <v>501</v>
+        <v>170.0197386934674</v>
       </c>
       <c r="M23" t="n">
         <v>501</v>
@@ -36423,7 +36423,7 @@
         <v>154.6425278990171</v>
       </c>
       <c r="Q23" t="n">
-        <v>21.38881815010336</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36484,10 +36484,10 @@
         <v>179.670757181072</v>
       </c>
       <c r="K24" t="n">
-        <v>275.1278864177303</v>
+        <v>284.1883452068291</v>
       </c>
       <c r="L24" t="n">
-        <v>399.2549602543474</v>
+        <v>390.1945014652479</v>
       </c>
       <c r="M24" t="n">
         <v>233.0100421645043</v>
@@ -36636,7 +36636,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>26.00497976626489</v>
       </c>
       <c r="J26" t="n">
         <v>56.39886310164335</v>
@@ -36660,7 +36660,7 @@
         <v>154.6425278990171</v>
       </c>
       <c r="Q26" t="n">
-        <v>26.00497976626491</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36718,28 +36718,28 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>96.20601525328352</v>
+        <v>164.0000000000228</v>
       </c>
       <c r="K27" t="n">
-        <v>132.3081043438156</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>164</v>
+        <v>155.1656237945493</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>61.03787987617005</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>164</v>
+        <v>121.7036805564146</v>
       </c>
       <c r="P27" t="n">
-        <v>4.592500221273568</v>
+        <v>164.0000000000228</v>
       </c>
       <c r="Q27" t="n">
-        <v>27.2292376791946</v>
+        <v>44.50443302272797</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36873,7 +36873,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2.093873897216312</v>
+        <v>2.09387389721594</v>
       </c>
       <c r="J29" t="n">
         <v>56.39886310164335</v>
@@ -36885,7 +36885,7 @@
         <v>164</v>
       </c>
       <c r="M29" t="n">
-        <v>23.91110586904858</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -36897,7 +36897,7 @@
         <v>154.6425278990171</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>23.91110586904895</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36955,25 +36955,25 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
+        <v>157.3737373737073</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>164</v>
       </c>
-      <c r="K30" t="n">
-        <v>141.6156133579145</v>
-      </c>
-      <c r="L30" t="n">
-        <v>11.16562379454928</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>164</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
       <c r="O30" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>4.592500221273568</v>
+        <v>164.0000000000301</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -37110,10 +37110,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>2.093873897216511</v>
       </c>
       <c r="J32" t="n">
-        <v>56.39886310164335</v>
+        <v>80.30996897069173</v>
       </c>
       <c r="K32" t="n">
         <v>137.0476582914573</v>
@@ -37125,7 +37125,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>26.00497976626486</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>111.2797083153548</v>
@@ -37192,25 +37192,25 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>164.0000000000374</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>141.6156133578771</v>
       </c>
       <c r="L33" t="n">
-        <v>157.3737373737374</v>
+        <v>11.16562379454928</v>
       </c>
       <c r="M33" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>164</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="P33" t="n">
-        <v>164</v>
+        <v>4.592500221273568</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37359,10 +37359,10 @@
         <v>164</v>
       </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>26.00497976626486</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>111.2797083153548</v>
@@ -37435,7 +37435,7 @@
         <v>164</v>
       </c>
       <c r="L36" t="n">
-        <v>11.16562379454928</v>
+        <v>152.7812371524638</v>
       </c>
       <c r="M36" t="n">
         <v>164</v>
@@ -37444,13 +37444,13 @@
         <v>164</v>
       </c>
       <c r="O36" t="n">
-        <v>137.6846614188013</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>4.592500221273568</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.930951939113328</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37596,7 +37596,7 @@
         <v>164</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>16.64750766523001</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -37605,10 +37605,10 @@
         <v>111.2797083153548</v>
       </c>
       <c r="P38" t="n">
-        <v>154.6425278990171</v>
+        <v>164.0000000000519</v>
       </c>
       <c r="Q38" t="n">
-        <v>26.00497976626491</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37666,7 +37666,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>164</v>
@@ -37675,7 +37675,7 @@
         <v>164</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -37684,10 +37684,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>157.3737373737374</v>
+        <v>153.4427854346235</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.930951939113882</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37827,7 +37827,7 @@
         <v>56.39886310164335</v>
       </c>
       <c r="K41" t="n">
-        <v>137.0476582914573</v>
+        <v>163.0526380577222</v>
       </c>
       <c r="L41" t="n">
         <v>164</v>
@@ -37845,7 +37845,7 @@
         <v>154.6425278990171</v>
       </c>
       <c r="Q41" t="n">
-        <v>26.00497976626491</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37906,25 +37906,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>164</v>
+        <v>65.61561335791455</v>
       </c>
       <c r="L42" t="n">
         <v>131.1656237945493</v>
       </c>
       <c r="M42" t="n">
-        <v>110.4583601240471</v>
+        <v>164</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>115.9280155546729</v>
+        <v>164</v>
       </c>
       <c r="P42" t="n">
         <v>124.5925002212736</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.229237679194597</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -38064,7 +38064,7 @@
         <v>56.39886310164335</v>
       </c>
       <c r="K44" t="n">
-        <v>137.0476582914573</v>
+        <v>163.0526380577222</v>
       </c>
       <c r="L44" t="n">
         <v>164</v>
@@ -38082,7 +38082,7 @@
         <v>154.6425278990171</v>
       </c>
       <c r="Q44" t="n">
-        <v>26.00497976626491</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,25 +38140,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>164.0000000000738</v>
       </c>
       <c r="K45" t="n">
-        <v>69.61561335791451</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>47.16562379454928</v>
+        <v>11.16562379454928</v>
       </c>
       <c r="M45" t="n">
-        <v>164</v>
+        <v>146.2081135790406</v>
       </c>
       <c r="N45" t="n">
         <v>164</v>
       </c>
       <c r="O45" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>40.59250022127357</v>
+        <v>164.0000000000738</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
